--- a/results/GEMV_Hardware_Results.xlsx
+++ b/results/GEMV_Hardware_Results.xlsx
@@ -13,16 +13,19 @@
     <sheet name="power_raw" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="325 MHz" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="power_raw_325" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Methodology" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="dense_300MHz" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="sparse_2to4_300MHz" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="sparse_2to8_300MHz" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="sparse_2to16_300MHz" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="sparse_2to32_300MHz" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="sparse_2to4_225MHz" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="sparse_2to8_225MHz" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="sparse_2to16_225MHz" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="sparse_2to32_225MHz" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Mixed sparsity" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Master table" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Floorplan SLR" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Methodology" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="dense_300MHz" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="sparse_2to4_300MHz" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="sparse_2to8_300MHz" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="sparse_2to16_300MHz" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="sparse_2to32_300MHz" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="sparse_2to4_225MHz" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="sparse_2to8_225MHz" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="sparse_2to16_225MHz" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="sparse_2to32_225MHz" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +34,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="11">
+  <numFmts count="13">
     <numFmt numFmtId="164" formatCode="0.0##"/>
     <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
@@ -43,6 +46,8 @@
     <numFmt numFmtId="172" formatCode="+0.0%;-0.0%"/>
     <numFmt numFmtId="173" formatCode="0.0000"/>
     <numFmt numFmtId="174" formatCode="+0.00%;-0.00%"/>
+    <numFmt numFmtId="175" formatCode="0.000%"/>
+    <numFmt numFmtId="176" formatCode="0.####"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -133,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -183,6 +188,14 @@
     <xf numFmtId="169" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="175" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -190,7 +203,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1210,469 +1222,272 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:A42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="118" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>two2N sparsity 2:8 @ 300 MHz (floorplanned build)  -  source: sparse_2to8_300MHz.csv</t>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="49" t="inlineStr">
+        <is>
+          <t>GEMV hardware measurement - method and caveats</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="43" t="inlineStr">
-        <is>
-          <t>Rows 'a-&gt;b' are differentials between adjacent sizes (launch overhead cancels). Row 'FIT' is the least-squares fit: Best us = FIXED OVERHEAD, Mean us = slope in us/beat, Worst us = R^2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Size / pair</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Weight beats</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Rows</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Best us</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Mean us</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Worst us</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Spread %</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Reps</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>Ideal us</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>Bytes in</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>of which index</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>Bytes out</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>Mrow/s</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>GB/s</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>beats/cycle</t>
+      <c r="A2" s="24" t="inlineStr"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="50" t="inlineStr">
+        <is>
+          <t>PLATFORM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44" customHeight="1">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>Alveo U280 (xcu280-fsvh2892-2L-e), platform xilinx_u280_xdma_201920_3, Vitis/Vivado 2021.1, XRT 2.13. Shared machine - the card is reprogrammed by other users between sessions.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="B5" s="25" t="n">
-        <v>262144</v>
-      </c>
-      <c r="C5" s="25" t="n">
-        <v>131072</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>1364.198</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>1570.222</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>1710.873</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="I5" s="11" t="n">
-        <v>873.813</v>
-      </c>
-      <c r="J5" s="25" t="n">
-        <v>92276736</v>
-      </c>
-      <c r="K5" s="25" t="n">
-        <v>25165824</v>
-      </c>
-      <c r="L5" s="25" t="n">
-        <v>262144</v>
-      </c>
-      <c r="M5" s="11" t="n">
-        <v>96.07989999999999</v>
-      </c>
-      <c r="N5" s="11" t="n">
-        <v>67.8339</v>
-      </c>
-      <c r="O5" s="11" t="n">
-        <v>0.6405</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>4096</t>
-        </is>
-      </c>
-      <c r="B6" s="25" t="n">
-        <v>524288</v>
-      </c>
-      <c r="C6" s="25" t="n">
-        <v>262144</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>2436.44</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>2599.144</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>3104.146</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="I6" s="11" t="n">
-        <v>1747.627</v>
-      </c>
-      <c r="J6" s="25" t="n">
-        <v>184551424</v>
-      </c>
-      <c r="K6" s="25" t="n">
-        <v>50331648</v>
-      </c>
-      <c r="L6" s="25" t="n">
-        <v>524288</v>
-      </c>
-      <c r="M6" s="11" t="n">
-        <v>107.593</v>
-      </c>
-      <c r="N6" s="11" t="n">
-        <v>75.9615</v>
-      </c>
-      <c r="O6" s="11" t="n">
-        <v>0.7173</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>8192</t>
-        </is>
-      </c>
-      <c r="B7" s="25" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="C7" s="25" t="n">
-        <v>524288</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>4210.27</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>4335.198</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>4527.631</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>3495.253</v>
-      </c>
-      <c r="J7" s="25" t="n">
-        <v>369100800</v>
-      </c>
-      <c r="K7" s="25" t="n">
-        <v>100663296</v>
-      </c>
-      <c r="L7" s="25" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="M7" s="11" t="n">
-        <v>124.526</v>
-      </c>
-      <c r="N7" s="11" t="n">
-        <v>87.9158</v>
-      </c>
-      <c r="O7" s="11" t="n">
-        <v>0.8302</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>16384</t>
-        </is>
-      </c>
-      <c r="B8" s="25" t="n">
-        <v>2097152</v>
-      </c>
-      <c r="C8" s="25" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>7693.22</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>7871.571</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>8064.237</v>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="I8" s="11" t="n">
-        <v>6990.507</v>
-      </c>
-      <c r="J8" s="25" t="n">
-        <v>738199552</v>
-      </c>
-      <c r="K8" s="25" t="n">
-        <v>201326592</v>
-      </c>
-      <c r="L8" s="25" t="n">
-        <v>2097152</v>
-      </c>
-      <c r="M8" s="11" t="n">
-        <v>136.2987</v>
-      </c>
-      <c r="N8" s="11" t="n">
-        <v>96.2272</v>
-      </c>
-      <c r="O8" s="11" t="n">
-        <v>0.9087</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="44" t="inlineStr">
-        <is>
-          <t>2048-&gt;4096</t>
-        </is>
-      </c>
-      <c r="B9" s="45" t="n">
-        <v>262144</v>
-      </c>
-      <c r="C9" s="45" t="n">
-        <v>131072</v>
-      </c>
-      <c r="D9" s="46" t="n">
-        <v>1072.242</v>
-      </c>
-      <c r="E9" s="46" t="inlineStr"/>
-      <c r="F9" s="46" t="inlineStr"/>
-      <c r="G9" s="46" t="inlineStr"/>
-      <c r="H9" s="47" t="inlineStr"/>
-      <c r="I9" s="46" t="n">
-        <v>873.813</v>
-      </c>
-      <c r="J9" s="45" t="n">
-        <v>92274688</v>
-      </c>
-      <c r="K9" s="45" t="n">
-        <v>25165824</v>
-      </c>
-      <c r="L9" s="45" t="n">
-        <v>262144</v>
-      </c>
-      <c r="M9" s="46" t="n">
-        <v>122.2411</v>
-      </c>
-      <c r="N9" s="46" t="n">
-        <v>86.3022</v>
-      </c>
-      <c r="O9" s="46" t="n">
-        <v>0.8149</v>
+      <c r="A5" s="24" t="inlineStr"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="50" t="inlineStr">
+        <is>
+          <t>SYSTEM UNDER TEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>dense : 10 x krnl_mm2s -&gt; krnl_gemv_dense (ap_ctrl_none, free-running) -&gt; 4 x krnl_s2mm. 14 HBM pseudo-channels. 300 MHz, WNS +0.022 ns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>sparse: 13 x krnl_mm2s -&gt; krnl_gemv_sparse -&gt; 4 x krnl_s2mm. 17 HBM pseudo-channels (8 weight + 3 index + 2 activation in, 4 out). 300 MHz, WNS 0.000 ns - a genuine pass (zero failing endpoints) but with NO margin, which should be stated as such.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>The data-mover kernels are the SAME BINARIES in both systems - not rebuilt - so the comparison isolates the compute engine.</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="44" t="inlineStr">
-        <is>
-          <t>4096-&gt;8192</t>
-        </is>
-      </c>
-      <c r="B10" s="45" t="n">
-        <v>524288</v>
-      </c>
-      <c r="C10" s="45" t="n">
-        <v>262144</v>
-      </c>
-      <c r="D10" s="46" t="n">
-        <v>1773.83</v>
-      </c>
-      <c r="E10" s="46" t="inlineStr"/>
-      <c r="F10" s="46" t="inlineStr"/>
-      <c r="G10" s="46" t="inlineStr"/>
-      <c r="H10" s="47" t="inlineStr"/>
-      <c r="I10" s="46" t="n">
-        <v>1747.627</v>
-      </c>
-      <c r="J10" s="45" t="n">
-        <v>184549376</v>
-      </c>
-      <c r="K10" s="45" t="n">
-        <v>50331648</v>
-      </c>
-      <c r="L10" s="45" t="n">
-        <v>524288</v>
-      </c>
-      <c r="M10" s="46" t="n">
-        <v>147.7842</v>
-      </c>
-      <c r="N10" s="46" t="n">
-        <v>104.3356</v>
-      </c>
-      <c r="O10" s="46" t="n">
-        <v>0.9852</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="44" t="inlineStr">
-        <is>
-          <t>8192-&gt;16384</t>
-        </is>
-      </c>
-      <c r="B11" s="45" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="C11" s="45" t="n">
-        <v>524288</v>
-      </c>
-      <c r="D11" s="46" t="n">
-        <v>3482.95</v>
-      </c>
-      <c r="E11" s="46" t="inlineStr"/>
-      <c r="F11" s="46" t="inlineStr"/>
-      <c r="G11" s="46" t="inlineStr"/>
-      <c r="H11" s="47" t="inlineStr"/>
-      <c r="I11" s="46" t="n">
-        <v>3495.253</v>
-      </c>
-      <c r="J11" s="45" t="n">
-        <v>369098752</v>
-      </c>
-      <c r="K11" s="45" t="n">
-        <v>100663296</v>
-      </c>
-      <c r="L11" s="45" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="M11" s="46" t="n">
-        <v>150.5299</v>
-      </c>
-      <c r="N11" s="46" t="n">
-        <v>106.2741</v>
-      </c>
-      <c r="O11" s="46" t="n">
-        <v>1.0035</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="30" t="inlineStr">
-        <is>
-          <t>FIT</t>
-        </is>
-      </c>
-      <c r="B12" s="48" t="inlineStr"/>
-      <c r="C12" s="48" t="inlineStr"/>
-      <c r="D12" s="49" t="n">
-        <v>569.497</v>
-      </c>
-      <c r="E12" s="50" t="n">
-        <v>0.00341444</v>
-      </c>
-      <c r="F12" s="51" t="n">
-        <v>0.99909</v>
-      </c>
-      <c r="G12" s="49" t="inlineStr"/>
-      <c r="H12" s="52" t="n">
-        <v>4</v>
-      </c>
-      <c r="I12" s="49" t="inlineStr"/>
-      <c r="J12" s="48" t="inlineStr"/>
-      <c r="K12" s="48" t="inlineStr"/>
-      <c r="L12" s="48" t="inlineStr"/>
-      <c r="M12" s="49" t="n">
-        <v>146.4367</v>
-      </c>
-      <c r="N12" s="49" t="n">
-        <v>103.3843</v>
-      </c>
-      <c r="O12" s="49" t="n">
-        <v>0.9762</v>
+      <c r="A10" s="24" t="inlineStr"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="50" t="inlineStr">
+        <is>
+          <t>WHY RAW PER-RUN NUMBERS ARE NOT QUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>A single run is dominated by XRT launch overhead: the first sparse hardware run measured a 460 us kernel span for TWO weight beats, ~99.99% scheduling. The fitted intercepts put the fixed overhead at 458-686 us regardless of design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="inlineStr"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="50" t="inlineStr">
+        <is>
+          <t>METHOD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>1. Four problem sizes spanning an IDENTICAL beat range in every configuration: 262,144 -&gt; 2,097,152 weight beats.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>2. Each size run 15-25 times (sparse) / 5 (dense); the BEST kernel span is kept. Best, not mean: the machine is shared, so slow samples are contention rather than the design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>3. Timing from OpenCL profiling events on the kernels (earliest CU start -&gt; latest CU end), never wall clock - loading an xclbin triggers FPGA reconfiguration, which is seconds and non-deterministic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>4. A least-squares fit t(beats) = overhead + beats x slope over all four sizes. The SLOPE is the marginal cost per beat and is what every headline figure derives from; the INTERCEPT is the fixed launch overhead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="44" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>5. Differential rows in the per-design sheets are the same quantity from adjacent size pairs only. They agree with the fit but are noisier - several report beats/cycle marginally ABOVE 1.0, which is physically impossible and is best-of estimator optimism on a single lucky sample, not a real measurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="50" t="inlineStr">
+        <is>
+          <t>CORRECTNESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="44" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>Throughput stimulus is synthetic and carries NO golden model - it exists only to generate beats. That is legitimate because the datapath's timing is data-independent: the gather is a mux (delay independent of which index it selects), the Xilinx FP operators are configured with Maximum_Latency, and there is no data-dependent control flow. Only beat COUNTS affect run length.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="44" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>Correctness is established separately, on small cases, by the Python golden model - bit-exact on hardware at all four sparsities AND in a runtime-reconfiguration run where the sparsity changes three times mid-calculation with no reload. Re-verified on the 300 MHz bitstream before any number here was recorded. The same golden model validated behavioural simulation, post-implementation simulation, hardware emulation and silicon, unchanged throughout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="50" t="inlineStr">
+        <is>
+          <t>A HYPOTHESIS THAT WAS WRONG - recorded so it is not repeated</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="44" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>An earlier, noisier sweep (smaller sizes, 5 reps, 30-60% spreads) showed beats/cycle apparently FALLING with sparsity - 0.969 / 0.831 / 0.879 / 0.787 - and this was attributed to the output path saturating at 2:32, where the freeze is 1 cycle so a flush occurs every cycle. That was MEASUREMENT NOISE, not an effect. Re-measured properly it is flat and near roofline at both clocks. There is no output-path bottleneck. The tell was present and missed: three differential rows in that data reported beats/cycle above 1.0, which is impossible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="50" t="inlineStr">
+        <is>
+          <t>POWER MEASUREMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="44" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>One calculation lasts 7-8 ms while `xbutil examine` takes ~1 s, so a 1 Hz instrument cannot sample a single run - and a plain run is ~85% H2D transfer anyway. Both hosts therefore take a soak argument: re-enqueue every CU back-to-back for 60 s with buffers ALREADY RESIDENT (no transfers), printing the window as epoch seconds so the sampler clips to exactly the load. ~54 samples per run survive the 6 s warm-up trim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="44" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>The warm-up trim is not cosmetic: on a 5 s trial a sample taken just after the load began read 28.94 W, BELOW the 29.30 W idle mean, because the card's satellite controller polls its sensors slowly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="44" customHeight="1">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>The idle baseline is taken AFTER the host exits, with the same bitstream still programmed - so leakage, clock trees and the platform are held constant and the difference isolates the work. The reading taken BEFORE the host runs is NOT a valid baseline: it reflects whatever design was previously loaded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="44" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Board power = the two 12 V input rails; VCCINT = the FPGA core rail, a SUBSET of it downstream of the regulators. Verified: 12 V Aux + 12 V PCIe reconstruct the reported board total exactly. Never sum the three. Only 3 of the U280's 14 rails report current, so only those three yield power.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="44" customHeight="1">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Host/CPU power is deliberately NOT measured. The host does identical work in both cases - same movers, same transfers, same OpenCL calls - so it cannot discriminate between the designs, and reporting it would add a number that looks like evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="50" t="inlineStr">
+        <is>
+          <t>KNOWN CAVEATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="44" customHeight="1">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>* The 300 MHz sparse build closes with WNS exactly 0.000 ns - zero failing endpoints, but zero margin, against dense's +0.022. Correctness was re-verified on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="44" customHeight="1">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>* R^2 is 0.9988-0.9994 at 300 MHz, marginally below the 0.999 threshold for 2:16. The cause is the smallest size in each sweep (25-32% spread from launch-overhead variance against 4-5% at the largest); more repetitions do not fix it. Independent replicate runs agreeing to 0.4-1.4% are the better uncertainty estimate - see Clock study.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="44" customHeight="1">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>* V = 1024 elements (32 activation windows) throughout. Vector length was not swept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="44" customHeight="1">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>* The 225 MHz sparse figures come from a DIFFERENT bitstream (no floorplan). They are a valid second data point, not an alternative measurement of the same design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="44" customHeight="1">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>* Power sampling at ~1 Hz measures STEADY STATE only; nothing transient is visible. Board power also includes fans, which are thermally controlled and drift.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="44" customHeight="1">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>* The dynamic power deltas (4-5 W) are differences of large numbers (~31-35 W) and are the least precise quantity reported. Standard errors are in the raw CSV and should be quoted with them. The energy-per-row figures, which divide a LOAD power by a measured throughput, are far better conditioned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="44" customHeight="1">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>* Dense was measured twice; dense_300MHz.csv is the run used here. An earlier run recorded in .claude/memory/INTEGRATION_STEPS.md S22 gives a 38.17 Mrow/s DIFFERENTIAL. Use the FIT (36.99), because every sparse figure is a fit and mixing estimators across the two sides of a comparison is indefensible. They agree on the physics (~1 beat/cycle).</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1709,12 +1524,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>two2N sparsity 2:16 @ 300 MHz (floorplanned build)  -  source: sparse_2to16_300MHz.csv</t>
+          <t>dense_gemv @ 300 MHz  -  source: dense_300MHz.csv</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="51" t="inlineStr">
         <is>
           <t>Rows 'a-&gt;b' are differentials between adjacent sizes (launch overhead cancels). Row 'FIT' is the least-squares fit: Best us = FIXED OVERHEAD, Mean us = slope in us/beat, Worst us = R^2.</t>
         </is>
@@ -1800,320 +1615,306 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>512</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>262144</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>262144</v>
+        <v>32768</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>1389.855</v>
+        <v>1350.042</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>1618.175</v>
+        <v>1378.399</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>1830.809</v>
+        <v>1420.373</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>31.7</v>
+        <v>5.2</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I5" s="11" t="n">
         <v>873.813</v>
       </c>
       <c r="J5" s="25" t="n">
-        <v>92276736</v>
-      </c>
-      <c r="K5" s="25" t="n">
-        <v>25165824</v>
-      </c>
+        <v>67110912</v>
+      </c>
+      <c r="K5" s="25" t="inlineStr"/>
       <c r="L5" s="25" t="n">
-        <v>524288</v>
+        <v>65536</v>
       </c>
       <c r="M5" s="11" t="n">
-        <v>188.6125</v>
+        <v>24.2718</v>
       </c>
       <c r="N5" s="11" t="n">
-        <v>66.77030000000001</v>
+        <v>49.7588</v>
       </c>
       <c r="O5" s="11" t="n">
-        <v>0.6287</v>
+        <v>0.6472</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>524288</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>524288</v>
+        <v>65536</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>2500.827</v>
+        <v>2248.313</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>2570.598</v>
+        <v>2343.055</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>2721.942</v>
+        <v>2509.826</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>8.800000000000001</v>
+        <v>11.6</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I6" s="11" t="n">
         <v>1747.627</v>
       </c>
       <c r="J6" s="25" t="n">
-        <v>184551424</v>
-      </c>
-      <c r="K6" s="25" t="n">
-        <v>50331648</v>
-      </c>
+        <v>134219776</v>
+      </c>
+      <c r="K6" s="25" t="inlineStr"/>
       <c r="L6" s="25" t="n">
-        <v>1048576</v>
+        <v>131072</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>209.6458</v>
+        <v>29.149</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>74.2154</v>
+        <v>59.7563</v>
       </c>
       <c r="O6" s="11" t="n">
-        <v>0.6988</v>
+        <v>0.7773</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>16384</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1048576</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>1048576</v>
+        <v>131072</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>4271.979</v>
+        <v>3962.545</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>4367.235</v>
+        <v>4106.829</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>4522.443</v>
+        <v>4211.676</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I7" s="11" t="n">
         <v>3495.253</v>
       </c>
       <c r="J7" s="25" t="n">
-        <v>369100800</v>
-      </c>
-      <c r="K7" s="25" t="n">
-        <v>100663296</v>
-      </c>
+        <v>268437504</v>
+      </c>
+      <c r="K7" s="25" t="inlineStr"/>
       <c r="L7" s="25" t="n">
-        <v>2097152</v>
+        <v>262144</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>245.4544</v>
+        <v>33.0777</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>86.8913</v>
+        <v>67.8099</v>
       </c>
       <c r="O7" s="11" t="n">
-        <v>0.8182</v>
+        <v>0.8821</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>2097152</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>2097152</v>
+        <v>262144</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>7777.355</v>
+        <v>7559.144</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>7922.982</v>
+        <v>7621.513</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>8111.325</v>
+        <v>7669.501</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I8" s="11" t="n">
         <v>6990.507</v>
       </c>
       <c r="J8" s="25" t="n">
-        <v>738199552</v>
-      </c>
-      <c r="K8" s="25" t="n">
-        <v>201326592</v>
-      </c>
+        <v>536872960</v>
+      </c>
+      <c r="K8" s="25" t="inlineStr"/>
       <c r="L8" s="25" t="n">
-        <v>4194304</v>
+        <v>524288</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>269.6485</v>
+        <v>34.6791</v>
       </c>
       <c r="N8" s="11" t="n">
-        <v>95.4558</v>
+        <v>71.09229999999999</v>
       </c>
       <c r="O8" s="11" t="n">
-        <v>0.8988</v>
+        <v>0.9248</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="44" t="inlineStr">
-        <is>
-          <t>4096-&gt;8192</t>
-        </is>
-      </c>
-      <c r="B9" s="45" t="n">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>512-&gt;1024</t>
+        </is>
+      </c>
+      <c r="B9" s="52" t="n">
         <v>262144</v>
       </c>
-      <c r="C9" s="45" t="n">
+      <c r="C9" s="52" t="n">
+        <v>32768</v>
+      </c>
+      <c r="D9" s="53" t="n">
+        <v>898.271</v>
+      </c>
+      <c r="E9" s="53" t="inlineStr"/>
+      <c r="F9" s="53" t="inlineStr"/>
+      <c r="G9" s="53" t="inlineStr"/>
+      <c r="H9" s="54" t="inlineStr"/>
+      <c r="I9" s="53" t="n">
+        <v>873.813</v>
+      </c>
+      <c r="J9" s="52" t="n">
+        <v>67108864</v>
+      </c>
+      <c r="K9" s="52" t="inlineStr"/>
+      <c r="L9" s="52" t="n">
+        <v>65536</v>
+      </c>
+      <c r="M9" s="53" t="n">
+        <v>36.479</v>
+      </c>
+      <c r="N9" s="53" t="n">
+        <v>74.78189999999999</v>
+      </c>
+      <c r="O9" s="53" t="n">
+        <v>0.9728</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>1024-&gt;2048</t>
+        </is>
+      </c>
+      <c r="B10" s="52" t="n">
+        <v>524288</v>
+      </c>
+      <c r="C10" s="52" t="n">
+        <v>65536</v>
+      </c>
+      <c r="D10" s="53" t="n">
+        <v>1714.232</v>
+      </c>
+      <c r="E10" s="53" t="inlineStr"/>
+      <c r="F10" s="53" t="inlineStr"/>
+      <c r="G10" s="53" t="inlineStr"/>
+      <c r="H10" s="54" t="inlineStr"/>
+      <c r="I10" s="53" t="n">
+        <v>1747.627</v>
+      </c>
+      <c r="J10" s="52" t="n">
+        <v>134217728</v>
+      </c>
+      <c r="K10" s="52" t="inlineStr"/>
+      <c r="L10" s="52" t="n">
+        <v>131072</v>
+      </c>
+      <c r="M10" s="53" t="n">
+        <v>38.2305</v>
+      </c>
+      <c r="N10" s="53" t="n">
+        <v>78.37260000000001</v>
+      </c>
+      <c r="O10" s="53" t="n">
+        <v>1.0195</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>2048-&gt;4096</t>
+        </is>
+      </c>
+      <c r="B11" s="52" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="C11" s="52" t="n">
+        <v>131072</v>
+      </c>
+      <c r="D11" s="53" t="n">
+        <v>3596.599</v>
+      </c>
+      <c r="E11" s="53" t="inlineStr"/>
+      <c r="F11" s="53" t="inlineStr"/>
+      <c r="G11" s="53" t="inlineStr"/>
+      <c r="H11" s="54" t="inlineStr"/>
+      <c r="I11" s="53" t="n">
+        <v>3495.253</v>
+      </c>
+      <c r="J11" s="52" t="n">
+        <v>268435456</v>
+      </c>
+      <c r="K11" s="52" t="inlineStr"/>
+      <c r="L11" s="52" t="n">
         <v>262144</v>
       </c>
-      <c r="D9" s="46" t="n">
-        <v>1110.972</v>
-      </c>
-      <c r="E9" s="46" t="inlineStr"/>
-      <c r="F9" s="46" t="inlineStr"/>
-      <c r="G9" s="46" t="inlineStr"/>
-      <c r="H9" s="47" t="inlineStr"/>
-      <c r="I9" s="46" t="n">
-        <v>873.813</v>
-      </c>
-      <c r="J9" s="45" t="n">
-        <v>92274688</v>
-      </c>
-      <c r="K9" s="45" t="n">
-        <v>25165824</v>
-      </c>
-      <c r="L9" s="45" t="n">
-        <v>524288</v>
-      </c>
-      <c r="M9" s="46" t="n">
-        <v>235.9591</v>
-      </c>
-      <c r="N9" s="46" t="n">
-        <v>83.5295</v>
-      </c>
-      <c r="O9" s="46" t="n">
-        <v>0.7865</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="44" t="inlineStr">
-        <is>
-          <t>8192-&gt;16384</t>
-        </is>
-      </c>
-      <c r="B10" s="45" t="n">
-        <v>524288</v>
-      </c>
-      <c r="C10" s="45" t="n">
-        <v>524288</v>
-      </c>
-      <c r="D10" s="46" t="n">
-        <v>1771.152</v>
-      </c>
-      <c r="E10" s="46" t="inlineStr"/>
-      <c r="F10" s="46" t="inlineStr"/>
-      <c r="G10" s="46" t="inlineStr"/>
-      <c r="H10" s="47" t="inlineStr"/>
-      <c r="I10" s="46" t="n">
-        <v>1747.627</v>
-      </c>
-      <c r="J10" s="45" t="n">
-        <v>184549376</v>
-      </c>
-      <c r="K10" s="45" t="n">
-        <v>50331648</v>
-      </c>
-      <c r="L10" s="45" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="M10" s="46" t="n">
-        <v>296.0152</v>
-      </c>
-      <c r="N10" s="46" t="n">
-        <v>104.7894</v>
-      </c>
-      <c r="O10" s="46" t="n">
-        <v>0.9867</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="44" t="inlineStr">
-        <is>
-          <t>16384-&gt;32768</t>
-        </is>
-      </c>
-      <c r="B11" s="45" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="C11" s="45" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="D11" s="46" t="n">
-        <v>3505.376</v>
-      </c>
-      <c r="E11" s="46" t="inlineStr"/>
-      <c r="F11" s="46" t="inlineStr"/>
-      <c r="G11" s="46" t="inlineStr"/>
-      <c r="H11" s="47" t="inlineStr"/>
-      <c r="I11" s="46" t="n">
-        <v>3495.253</v>
-      </c>
-      <c r="J11" s="45" t="n">
-        <v>369098752</v>
-      </c>
-      <c r="K11" s="45" t="n">
-        <v>100663296</v>
-      </c>
-      <c r="L11" s="45" t="n">
-        <v>2097152</v>
-      </c>
-      <c r="M11" s="46" t="n">
-        <v>299.1337</v>
-      </c>
-      <c r="N11" s="46" t="n">
-        <v>105.8933</v>
-      </c>
-      <c r="O11" s="46" t="n">
-        <v>0.9971</v>
+      <c r="M11" s="53" t="n">
+        <v>36.4433</v>
+      </c>
+      <c r="N11" s="53" t="n">
+        <v>74.7088</v>
+      </c>
+      <c r="O11" s="53" t="n">
+        <v>0.9718</v>
       </c>
     </row>
     <row r="12">
@@ -2122,33 +1923,33 @@
           <t>FIT</t>
         </is>
       </c>
-      <c r="B12" s="48" t="inlineStr"/>
-      <c r="C12" s="48" t="inlineStr"/>
-      <c r="D12" s="49" t="n">
-        <v>603.716</v>
-      </c>
-      <c r="E12" s="50" t="n">
-        <v>0.00343962</v>
-      </c>
-      <c r="F12" s="51" t="n">
-        <v>0.99882</v>
-      </c>
-      <c r="G12" s="49" t="inlineStr"/>
-      <c r="H12" s="52" t="n">
+      <c r="B12" s="55" t="inlineStr"/>
+      <c r="C12" s="55" t="inlineStr"/>
+      <c r="D12" s="56" t="n">
+        <v>457.859</v>
+      </c>
+      <c r="E12" s="57" t="n">
+        <v>0.00337947</v>
+      </c>
+      <c r="F12" s="58" t="n">
+        <v>0.99991</v>
+      </c>
+      <c r="G12" s="56" t="inlineStr"/>
+      <c r="H12" s="59" t="n">
         <v>4</v>
       </c>
-      <c r="I12" s="49" t="inlineStr"/>
-      <c r="J12" s="48" t="inlineStr"/>
-      <c r="K12" s="48" t="inlineStr"/>
-      <c r="L12" s="48" t="inlineStr"/>
-      <c r="M12" s="49" t="n">
-        <v>290.7295</v>
-      </c>
-      <c r="N12" s="49" t="n">
-        <v>102.9182</v>
-      </c>
-      <c r="O12" s="49" t="n">
-        <v>0.9691</v>
+      <c r="I12" s="56" t="inlineStr"/>
+      <c r="J12" s="55" t="inlineStr"/>
+      <c r="K12" s="55" t="inlineStr"/>
+      <c r="L12" s="55" t="inlineStr"/>
+      <c r="M12" s="56" t="n">
+        <v>36.9881</v>
+      </c>
+      <c r="N12" s="56" t="n">
+        <v>75.82550000000001</v>
+      </c>
+      <c r="O12" s="56" t="n">
+        <v>0.9863</v>
       </c>
     </row>
   </sheetData>
@@ -2185,12 +1986,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>two2N sparsity 2:32 @ 300 MHz (floorplanned build)  -  source: sparse_2to32_300MHz.csv</t>
+          <t>two2N sparsity 2:4 @ 300 MHz (floorplanned build)  -  source: sparse_2to4_300MHz.csv</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="51" t="inlineStr">
         <is>
           <t>Rows 'a-&gt;b' are differentials between adjacent sizes (launch overhead cancels). Row 'FIT' is the least-squares fit: Best us = FIXED OVERHEAD, Mean us = slope in us/beat, Worst us = R^2.</t>
         </is>
@@ -2276,26 +2077,26 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>262144</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>524288</v>
+        <v>65536</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>1498.933</v>
+        <v>1470.278</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>1629.342</v>
+        <v>1618.479</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>1782.194</v>
+        <v>1828.971</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>15</v>
@@ -2310,41 +2111,41 @@
         <v>25165824</v>
       </c>
       <c r="L5" s="25" t="n">
-        <v>1048576</v>
+        <v>131072</v>
       </c>
       <c r="M5" s="11" t="n">
-        <v>349.7741</v>
+        <v>44.5739</v>
       </c>
       <c r="N5" s="11" t="n">
-        <v>62.2612</v>
+        <v>62.8506</v>
       </c>
       <c r="O5" s="11" t="n">
-        <v>0.583</v>
+        <v>0.5943000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>16384</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>524288</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>1048576</v>
+        <v>131072</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>2570.294</v>
+        <v>2492.261</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>2629.207</v>
+        <v>2579.305</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>2690.06</v>
+        <v>2740.292</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>15</v>
@@ -2359,41 +2160,41 @@
         <v>50331648</v>
       </c>
       <c r="L6" s="25" t="n">
-        <v>2097152</v>
+        <v>262144</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>407.9596</v>
+        <v>52.5916</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>72.6176</v>
+        <v>74.155</v>
       </c>
       <c r="O6" s="11" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.7012</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1048576</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>2097152</v>
+        <v>262144</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>4369.453</v>
+        <v>4132.258</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>4435.333</v>
+        <v>4314.617</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>4530.465</v>
+        <v>4437.367</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>3.7</v>
+        <v>7.4</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>15</v>
@@ -2408,41 +2209,41 @@
         <v>100663296</v>
       </c>
       <c r="L7" s="25" t="n">
-        <v>4194304</v>
+        <v>524288</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>479.9576</v>
+        <v>63.4384</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>85.4329</v>
+        <v>89.4487</v>
       </c>
       <c r="O7" s="11" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.8458</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>65536</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>2097152</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>4194304</v>
+        <v>524288</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>7905.593</v>
+        <v>7774.47</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>8047.452</v>
+        <v>7839.704</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>8193.317999999999</v>
+        <v>7887.112</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>15</v>
@@ -2457,139 +2258,139 @@
         <v>201326592</v>
       </c>
       <c r="L8" s="25" t="n">
-        <v>8388608</v>
+        <v>1048576</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>530.5489</v>
+        <v>67.4371</v>
       </c>
       <c r="N8" s="11" t="n">
-        <v>94.438</v>
+        <v>95.0866</v>
       </c>
       <c r="O8" s="11" t="n">
-        <v>0.8842</v>
+        <v>0.8992</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="44" t="inlineStr">
-        <is>
-          <t>8192-&gt;16384</t>
-        </is>
-      </c>
-      <c r="B9" s="45" t="n">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>1024-&gt;2048</t>
+        </is>
+      </c>
+      <c r="B9" s="52" t="n">
         <v>262144</v>
       </c>
-      <c r="C9" s="45" t="n">
+      <c r="C9" s="52" t="n">
+        <v>65536</v>
+      </c>
+      <c r="D9" s="53" t="n">
+        <v>1021.983</v>
+      </c>
+      <c r="E9" s="53" t="inlineStr"/>
+      <c r="F9" s="53" t="inlineStr"/>
+      <c r="G9" s="53" t="inlineStr"/>
+      <c r="H9" s="54" t="inlineStr"/>
+      <c r="I9" s="53" t="n">
+        <v>873.813</v>
+      </c>
+      <c r="J9" s="52" t="n">
+        <v>92274688</v>
+      </c>
+      <c r="K9" s="52" t="n">
+        <v>25165824</v>
+      </c>
+      <c r="L9" s="52" t="n">
+        <v>131072</v>
+      </c>
+      <c r="M9" s="53" t="n">
+        <v>64.1263</v>
+      </c>
+      <c r="N9" s="53" t="n">
+        <v>90.4181</v>
+      </c>
+      <c r="O9" s="53" t="n">
+        <v>0.855</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>2048-&gt;4096</t>
+        </is>
+      </c>
+      <c r="B10" s="52" t="n">
         <v>524288</v>
       </c>
-      <c r="D9" s="46" t="n">
-        <v>1071.361</v>
-      </c>
-      <c r="E9" s="46" t="inlineStr"/>
-      <c r="F9" s="46" t="inlineStr"/>
-      <c r="G9" s="46" t="inlineStr"/>
-      <c r="H9" s="47" t="inlineStr"/>
-      <c r="I9" s="46" t="n">
-        <v>873.813</v>
-      </c>
-      <c r="J9" s="45" t="n">
-        <v>92274688</v>
-      </c>
-      <c r="K9" s="45" t="n">
-        <v>25165824</v>
-      </c>
-      <c r="L9" s="45" t="n">
+      <c r="C10" s="52" t="n">
+        <v>131072</v>
+      </c>
+      <c r="D10" s="53" t="n">
+        <v>1639.997</v>
+      </c>
+      <c r="E10" s="53" t="inlineStr"/>
+      <c r="F10" s="53" t="inlineStr"/>
+      <c r="G10" s="53" t="inlineStr"/>
+      <c r="H10" s="54" t="inlineStr"/>
+      <c r="I10" s="53" t="n">
+        <v>1747.627</v>
+      </c>
+      <c r="J10" s="52" t="n">
+        <v>184549376</v>
+      </c>
+      <c r="K10" s="52" t="n">
+        <v>50331648</v>
+      </c>
+      <c r="L10" s="52" t="n">
+        <v>262144</v>
+      </c>
+      <c r="M10" s="53" t="n">
+        <v>79.9221</v>
+      </c>
+      <c r="N10" s="53" t="n">
+        <v>112.6902</v>
+      </c>
+      <c r="O10" s="53" t="n">
+        <v>1.0656</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>4096-&gt;8192</t>
+        </is>
+      </c>
+      <c r="B11" s="52" t="n">
         <v>1048576</v>
       </c>
-      <c r="M9" s="46" t="n">
-        <v>489.3663</v>
-      </c>
-      <c r="N9" s="46" t="n">
-        <v>87.10720000000001</v>
-      </c>
-      <c r="O9" s="46" t="n">
-        <v>0.8156</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="44" t="inlineStr">
-        <is>
-          <t>16384-&gt;32768</t>
-        </is>
-      </c>
-      <c r="B10" s="45" t="n">
+      <c r="C11" s="52" t="n">
+        <v>262144</v>
+      </c>
+      <c r="D11" s="53" t="n">
+        <v>3642.212</v>
+      </c>
+      <c r="E11" s="53" t="inlineStr"/>
+      <c r="F11" s="53" t="inlineStr"/>
+      <c r="G11" s="53" t="inlineStr"/>
+      <c r="H11" s="54" t="inlineStr"/>
+      <c r="I11" s="53" t="n">
+        <v>3495.253</v>
+      </c>
+      <c r="J11" s="52" t="n">
+        <v>369098752</v>
+      </c>
+      <c r="K11" s="52" t="n">
+        <v>100663296</v>
+      </c>
+      <c r="L11" s="52" t="n">
         <v>524288</v>
       </c>
-      <c r="C10" s="45" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="D10" s="46" t="n">
-        <v>1799.159</v>
-      </c>
-      <c r="E10" s="46" t="inlineStr"/>
-      <c r="F10" s="46" t="inlineStr"/>
-      <c r="G10" s="46" t="inlineStr"/>
-      <c r="H10" s="47" t="inlineStr"/>
-      <c r="I10" s="46" t="n">
-        <v>1747.627</v>
-      </c>
-      <c r="J10" s="45" t="n">
-        <v>184549376</v>
-      </c>
-      <c r="K10" s="45" t="n">
-        <v>50331648</v>
-      </c>
-      <c r="L10" s="45" t="n">
-        <v>2097152</v>
-      </c>
-      <c r="M10" s="46" t="n">
-        <v>582.8145</v>
-      </c>
-      <c r="N10" s="46" t="n">
-        <v>103.741</v>
-      </c>
-      <c r="O10" s="46" t="n">
-        <v>0.9714</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="44" t="inlineStr">
-        <is>
-          <t>32768-&gt;65536</t>
-        </is>
-      </c>
-      <c r="B11" s="45" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="C11" s="45" t="n">
-        <v>2097152</v>
-      </c>
-      <c r="D11" s="46" t="n">
-        <v>3536.14</v>
-      </c>
-      <c r="E11" s="46" t="inlineStr"/>
-      <c r="F11" s="46" t="inlineStr"/>
-      <c r="G11" s="46" t="inlineStr"/>
-      <c r="H11" s="47" t="inlineStr"/>
-      <c r="I11" s="46" t="n">
-        <v>3495.253</v>
-      </c>
-      <c r="J11" s="45" t="n">
-        <v>369098752</v>
-      </c>
-      <c r="K11" s="45" t="n">
-        <v>100663296</v>
-      </c>
-      <c r="L11" s="45" t="n">
-        <v>4194304</v>
-      </c>
-      <c r="M11" s="46" t="n">
-        <v>593.0625</v>
-      </c>
-      <c r="N11" s="46" t="n">
-        <v>105.5651</v>
-      </c>
-      <c r="O11" s="46" t="n">
-        <v>0.9883999999999999</v>
+      <c r="M11" s="53" t="n">
+        <v>71.9738</v>
+      </c>
+      <c r="N11" s="53" t="n">
+        <v>101.4831</v>
+      </c>
+      <c r="O11" s="53" t="n">
+        <v>0.9597</v>
       </c>
     </row>
     <row r="12">
@@ -2598,33 +2399,33 @@
           <t>FIT</t>
         </is>
       </c>
-      <c r="B12" s="48" t="inlineStr"/>
-      <c r="C12" s="48" t="inlineStr"/>
-      <c r="D12" s="49" t="n">
-        <v>685.496</v>
-      </c>
-      <c r="E12" s="50" t="n">
-        <v>0.00345924</v>
-      </c>
-      <c r="F12" s="51" t="n">
-        <v>0.99923</v>
-      </c>
-      <c r="G12" s="49" t="inlineStr"/>
-      <c r="H12" s="52" t="n">
+      <c r="B12" s="55" t="inlineStr"/>
+      <c r="C12" s="55" t="inlineStr"/>
+      <c r="D12" s="56" t="n">
+        <v>619.077</v>
+      </c>
+      <c r="E12" s="57" t="n">
+        <v>0.00340601</v>
+      </c>
+      <c r="F12" s="58" t="n">
+        <v>0.99944</v>
+      </c>
+      <c r="G12" s="56" t="inlineStr"/>
+      <c r="H12" s="59" t="n">
         <v>4</v>
       </c>
-      <c r="I12" s="49" t="inlineStr"/>
-      <c r="J12" s="48" t="inlineStr"/>
-      <c r="K12" s="48" t="inlineStr"/>
-      <c r="L12" s="48" t="inlineStr"/>
-      <c r="M12" s="49" t="n">
-        <v>578.1615</v>
-      </c>
-      <c r="N12" s="49" t="n">
-        <v>102.9128</v>
-      </c>
-      <c r="O12" s="49" t="n">
-        <v>0.9636</v>
+      <c r="I12" s="56" t="inlineStr"/>
+      <c r="J12" s="55" t="inlineStr"/>
+      <c r="K12" s="55" t="inlineStr"/>
+      <c r="L12" s="55" t="inlineStr"/>
+      <c r="M12" s="56" t="n">
+        <v>73.3998</v>
+      </c>
+      <c r="N12" s="56" t="n">
+        <v>103.4937</v>
+      </c>
+      <c r="O12" s="56" t="n">
+        <v>0.9787</v>
       </c>
     </row>
   </sheetData>
@@ -2661,12 +2462,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>two2N sparsity 2:4 @ 225 MHz (pre-floorplan build)  -  source: sparse_2to4_225MHz.csv</t>
+          <t>two2N sparsity 2:8 @ 300 MHz (floorplanned build)  -  source: sparse_2to8_300MHz.csv</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="51" t="inlineStr">
         <is>
           <t>Rows 'a-&gt;b' are differentials between adjacent sizes (launch overhead cancels). Row 'FIT' is the least-squares fit: Best us = FIXED OVERHEAD, Mean us = slope in us/beat, Worst us = R^2.</t>
         </is>
@@ -2752,32 +2553,32 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>262144</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>65536</v>
+        <v>131072</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>1744.379</v>
+        <v>1364.198</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>1844.359</v>
+        <v>1570.222</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2130.395</v>
+        <v>1710.873</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>22.1</v>
+        <v>25.4</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>1165.084</v>
+        <v>873.813</v>
       </c>
       <c r="J5" s="25" t="n">
         <v>92276736</v>
@@ -2786,47 +2587,47 @@
         <v>25165824</v>
       </c>
       <c r="L5" s="25" t="n">
-        <v>131072</v>
+        <v>262144</v>
       </c>
       <c r="M5" s="11" t="n">
-        <v>37.5698</v>
+        <v>96.07989999999999</v>
       </c>
       <c r="N5" s="11" t="n">
-        <v>52.9746</v>
+        <v>67.8339</v>
       </c>
       <c r="O5" s="11" t="n">
-        <v>0.6679</v>
+        <v>0.6405</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>524288</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>131072</v>
+        <v>262144</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>3023.539</v>
+        <v>2436.44</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>3141.519</v>
+        <v>2599.144</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>3292.324</v>
+        <v>3104.146</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>8.9</v>
+        <v>27.4</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>2330.169</v>
+        <v>1747.627</v>
       </c>
       <c r="J6" s="25" t="n">
         <v>184551424</v>
@@ -2835,47 +2636,47 @@
         <v>50331648</v>
       </c>
       <c r="L6" s="25" t="n">
-        <v>262144</v>
+        <v>524288</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>43.3505</v>
+        <v>107.593</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>61.1249</v>
+        <v>75.9615</v>
       </c>
       <c r="O6" s="11" t="n">
-        <v>0.7707000000000001</v>
+        <v>0.7173</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1048576</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>262144</v>
+        <v>524288</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>5240.044</v>
+        <v>4210.27</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>5444.641</v>
+        <v>4335.198</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>5715.295</v>
+        <v>4527.631</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>4660.338</v>
+        <v>3495.253</v>
       </c>
       <c r="J7" s="25" t="n">
         <v>369100800</v>
@@ -2884,47 +2685,47 @@
         <v>100663296</v>
       </c>
       <c r="L7" s="25" t="n">
-        <v>524288</v>
+        <v>1048576</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>50.0271</v>
+        <v>124.526</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>70.5385</v>
+        <v>87.9158</v>
       </c>
       <c r="O7" s="11" t="n">
-        <v>0.8894</v>
+        <v>0.8302</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>16384</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>2097152</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>524288</v>
+        <v>1048576</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>9977.441999999999</v>
+        <v>7693.22</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>10139.83</v>
+        <v>7871.571</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>10300.308</v>
+        <v>8064.237</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>9320.675999999999</v>
+        <v>6990.507</v>
       </c>
       <c r="J8" s="25" t="n">
         <v>738199552</v>
@@ -2933,139 +2734,139 @@
         <v>201326592</v>
       </c>
       <c r="L8" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="M8" s="11" t="n">
+        <v>136.2987</v>
+      </c>
+      <c r="N8" s="11" t="n">
+        <v>96.2272</v>
+      </c>
+      <c r="O8" s="11" t="n">
+        <v>0.9087</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>2048-&gt;4096</t>
+        </is>
+      </c>
+      <c r="B9" s="52" t="n">
+        <v>262144</v>
+      </c>
+      <c r="C9" s="52" t="n">
+        <v>131072</v>
+      </c>
+      <c r="D9" s="53" t="n">
+        <v>1072.242</v>
+      </c>
+      <c r="E9" s="53" t="inlineStr"/>
+      <c r="F9" s="53" t="inlineStr"/>
+      <c r="G9" s="53" t="inlineStr"/>
+      <c r="H9" s="54" t="inlineStr"/>
+      <c r="I9" s="53" t="n">
+        <v>873.813</v>
+      </c>
+      <c r="J9" s="52" t="n">
+        <v>92274688</v>
+      </c>
+      <c r="K9" s="52" t="n">
+        <v>25165824</v>
+      </c>
+      <c r="L9" s="52" t="n">
+        <v>262144</v>
+      </c>
+      <c r="M9" s="53" t="n">
+        <v>122.2411</v>
+      </c>
+      <c r="N9" s="53" t="n">
+        <v>86.3022</v>
+      </c>
+      <c r="O9" s="53" t="n">
+        <v>0.8149</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>4096-&gt;8192</t>
+        </is>
+      </c>
+      <c r="B10" s="52" t="n">
+        <v>524288</v>
+      </c>
+      <c r="C10" s="52" t="n">
+        <v>262144</v>
+      </c>
+      <c r="D10" s="53" t="n">
+        <v>1773.83</v>
+      </c>
+      <c r="E10" s="53" t="inlineStr"/>
+      <c r="F10" s="53" t="inlineStr"/>
+      <c r="G10" s="53" t="inlineStr"/>
+      <c r="H10" s="54" t="inlineStr"/>
+      <c r="I10" s="53" t="n">
+        <v>1747.627</v>
+      </c>
+      <c r="J10" s="52" t="n">
+        <v>184549376</v>
+      </c>
+      <c r="K10" s="52" t="n">
+        <v>50331648</v>
+      </c>
+      <c r="L10" s="52" t="n">
+        <v>524288</v>
+      </c>
+      <c r="M10" s="53" t="n">
+        <v>147.7842</v>
+      </c>
+      <c r="N10" s="53" t="n">
+        <v>104.3356</v>
+      </c>
+      <c r="O10" s="53" t="n">
+        <v>0.9852</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>8192-&gt;16384</t>
+        </is>
+      </c>
+      <c r="B11" s="52" t="n">
         <v>1048576</v>
       </c>
-      <c r="M8" s="11" t="n">
-        <v>52.5473</v>
-      </c>
-      <c r="N8" s="11" t="n">
-        <v>74.0919</v>
-      </c>
-      <c r="O8" s="11" t="n">
-        <v>0.9342</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="44" t="inlineStr">
-        <is>
-          <t>1024-&gt;2048</t>
-        </is>
-      </c>
-      <c r="B9" s="45" t="n">
-        <v>262144</v>
-      </c>
-      <c r="C9" s="45" t="n">
-        <v>65536</v>
-      </c>
-      <c r="D9" s="46" t="n">
-        <v>1279.16</v>
-      </c>
-      <c r="E9" s="46" t="inlineStr"/>
-      <c r="F9" s="46" t="inlineStr"/>
-      <c r="G9" s="46" t="inlineStr"/>
-      <c r="H9" s="47" t="inlineStr"/>
-      <c r="I9" s="46" t="n">
-        <v>1165.084</v>
-      </c>
-      <c r="J9" s="45" t="n">
-        <v>92274688</v>
-      </c>
-      <c r="K9" s="45" t="n">
-        <v>25165824</v>
-      </c>
-      <c r="L9" s="45" t="n">
-        <v>131072</v>
-      </c>
-      <c r="M9" s="46" t="n">
-        <v>51.2336</v>
-      </c>
-      <c r="N9" s="46" t="n">
-        <v>72.2394</v>
-      </c>
-      <c r="O9" s="46" t="n">
-        <v>0.9108000000000001</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="44" t="inlineStr">
-        <is>
-          <t>2048-&gt;4096</t>
-        </is>
-      </c>
-      <c r="B10" s="45" t="n">
+      <c r="C11" s="52" t="n">
         <v>524288</v>
       </c>
-      <c r="C10" s="45" t="n">
-        <v>131072</v>
-      </c>
-      <c r="D10" s="46" t="n">
-        <v>2216.505</v>
-      </c>
-      <c r="E10" s="46" t="inlineStr"/>
-      <c r="F10" s="46" t="inlineStr"/>
-      <c r="G10" s="46" t="inlineStr"/>
-      <c r="H10" s="47" t="inlineStr"/>
-      <c r="I10" s="46" t="n">
-        <v>2330.169</v>
-      </c>
-      <c r="J10" s="45" t="n">
-        <v>184549376</v>
-      </c>
-      <c r="K10" s="45" t="n">
-        <v>50331648</v>
-      </c>
-      <c r="L10" s="45" t="n">
-        <v>262144</v>
-      </c>
-      <c r="M10" s="46" t="n">
-        <v>59.1345</v>
-      </c>
-      <c r="N10" s="46" t="n">
-        <v>83.3797</v>
-      </c>
-      <c r="O10" s="46" t="n">
-        <v>1.0513</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="44" t="inlineStr">
-        <is>
-          <t>4096-&gt;8192</t>
-        </is>
-      </c>
-      <c r="B11" s="45" t="n">
+      <c r="D11" s="53" t="n">
+        <v>3482.95</v>
+      </c>
+      <c r="E11" s="53" t="inlineStr"/>
+      <c r="F11" s="53" t="inlineStr"/>
+      <c r="G11" s="53" t="inlineStr"/>
+      <c r="H11" s="54" t="inlineStr"/>
+      <c r="I11" s="53" t="n">
+        <v>3495.253</v>
+      </c>
+      <c r="J11" s="52" t="n">
+        <v>369098752</v>
+      </c>
+      <c r="K11" s="52" t="n">
+        <v>100663296</v>
+      </c>
+      <c r="L11" s="52" t="n">
         <v>1048576</v>
       </c>
-      <c r="C11" s="45" t="n">
-        <v>262144</v>
-      </c>
-      <c r="D11" s="46" t="n">
-        <v>4737.398</v>
-      </c>
-      <c r="E11" s="46" t="inlineStr"/>
-      <c r="F11" s="46" t="inlineStr"/>
-      <c r="G11" s="46" t="inlineStr"/>
-      <c r="H11" s="47" t="inlineStr"/>
-      <c r="I11" s="46" t="n">
-        <v>4660.338</v>
-      </c>
-      <c r="J11" s="45" t="n">
-        <v>369098752</v>
-      </c>
-      <c r="K11" s="45" t="n">
-        <v>100663296</v>
-      </c>
-      <c r="L11" s="45" t="n">
-        <v>524288</v>
-      </c>
-      <c r="M11" s="46" t="n">
-        <v>55.335</v>
-      </c>
-      <c r="N11" s="46" t="n">
-        <v>78.0224</v>
-      </c>
-      <c r="O11" s="46" t="n">
-        <v>0.9837</v>
+      <c r="M11" s="53" t="n">
+        <v>150.5299</v>
+      </c>
+      <c r="N11" s="53" t="n">
+        <v>106.2741</v>
+      </c>
+      <c r="O11" s="53" t="n">
+        <v>1.0035</v>
       </c>
     </row>
     <row r="12">
@@ -3074,33 +2875,33 @@
           <t>FIT</t>
         </is>
       </c>
-      <c r="B12" s="48" t="inlineStr"/>
-      <c r="C12" s="48" t="inlineStr"/>
-      <c r="D12" s="49" t="n">
-        <v>610.364</v>
-      </c>
-      <c r="E12" s="50" t="n">
-        <v>0.00446166</v>
-      </c>
-      <c r="F12" s="51" t="n">
-        <v>0.99977</v>
-      </c>
-      <c r="G12" s="49" t="inlineStr"/>
-      <c r="H12" s="52" t="n">
+      <c r="B12" s="55" t="inlineStr"/>
+      <c r="C12" s="55" t="inlineStr"/>
+      <c r="D12" s="56" t="n">
+        <v>569.497</v>
+      </c>
+      <c r="E12" s="57" t="n">
+        <v>0.00341444</v>
+      </c>
+      <c r="F12" s="58" t="n">
+        <v>0.99909</v>
+      </c>
+      <c r="G12" s="56" t="inlineStr"/>
+      <c r="H12" s="59" t="n">
         <v>4</v>
       </c>
-      <c r="I12" s="49" t="inlineStr"/>
-      <c r="J12" s="48" t="inlineStr"/>
-      <c r="K12" s="48" t="inlineStr"/>
-      <c r="L12" s="48" t="inlineStr"/>
-      <c r="M12" s="49" t="n">
-        <v>56.033</v>
-      </c>
-      <c r="N12" s="49" t="n">
-        <v>79.0065</v>
-      </c>
-      <c r="O12" s="49" t="n">
-        <v>0.9961</v>
+      <c r="I12" s="56" t="inlineStr"/>
+      <c r="J12" s="55" t="inlineStr"/>
+      <c r="K12" s="55" t="inlineStr"/>
+      <c r="L12" s="55" t="inlineStr"/>
+      <c r="M12" s="56" t="n">
+        <v>146.4367</v>
+      </c>
+      <c r="N12" s="56" t="n">
+        <v>103.3843</v>
+      </c>
+      <c r="O12" s="56" t="n">
+        <v>0.9762</v>
       </c>
     </row>
   </sheetData>
@@ -3137,12 +2938,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>two2N sparsity 2:8 @ 225 MHz (pre-floorplan build)  -  source: sparse_2to8_225MHz.csv</t>
+          <t>two2N sparsity 2:16 @ 300 MHz (floorplanned build)  -  source: sparse_2to16_300MHz.csv</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="51" t="inlineStr">
         <is>
           <t>Rows 'a-&gt;b' are differentials between adjacent sizes (launch overhead cancels). Row 'FIT' is the least-squares fit: Best us = FIXED OVERHEAD, Mean us = slope in us/beat, Worst us = R^2.</t>
         </is>
@@ -3228,32 +3029,32 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>262144</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>131072</v>
+        <v>262144</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>1769.391</v>
+        <v>1389.855</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>1871.982</v>
+        <v>1618.175</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2012.449</v>
+        <v>1830.809</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>13.7</v>
+        <v>31.7</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>1165.084</v>
+        <v>873.813</v>
       </c>
       <c r="J5" s="25" t="n">
         <v>92276736</v>
@@ -3262,47 +3063,47 @@
         <v>25165824</v>
       </c>
       <c r="L5" s="25" t="n">
-        <v>262144</v>
+        <v>524288</v>
       </c>
       <c r="M5" s="11" t="n">
-        <v>74.0775</v>
+        <v>188.6125</v>
       </c>
       <c r="N5" s="11" t="n">
-        <v>52.2998</v>
+        <v>66.77030000000001</v>
       </c>
       <c r="O5" s="11" t="n">
-        <v>0.6585</v>
+        <v>0.6287</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>524288</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>262144</v>
+        <v>524288</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>2907.638</v>
+        <v>2500.827</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>3105.124</v>
+        <v>2570.598</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>3211.361</v>
+        <v>2721.942</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>10.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>2330.169</v>
+        <v>1747.627</v>
       </c>
       <c r="J6" s="25" t="n">
         <v>184551424</v>
@@ -3311,47 +3112,47 @@
         <v>50331648</v>
       </c>
       <c r="L6" s="25" t="n">
-        <v>524288</v>
+        <v>1048576</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>90.157</v>
+        <v>209.6458</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>63.6516</v>
+        <v>74.2154</v>
       </c>
       <c r="O6" s="11" t="n">
-        <v>0.8014</v>
+        <v>0.6988</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>16384</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1048576</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>524288</v>
+        <v>1048576</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>5283.475</v>
+        <v>4271.979</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>5517.496</v>
+        <v>4367.235</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>5732.823</v>
+        <v>4522.443</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>8.5</v>
+        <v>5.9</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>4660.338</v>
+        <v>3495.253</v>
       </c>
       <c r="J7" s="25" t="n">
         <v>369100800</v>
@@ -3360,47 +3161,47 @@
         <v>100663296</v>
       </c>
       <c r="L7" s="25" t="n">
-        <v>1048576</v>
+        <v>2097152</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>99.2317</v>
+        <v>245.4544</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>70.0579</v>
+        <v>86.8913</v>
       </c>
       <c r="O7" s="11" t="n">
-        <v>0.8821</v>
+        <v>0.8182</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>16384</t>
+          <t>32768</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>2097152</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>1048576</v>
+        <v>2097152</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>10101.206</v>
+        <v>7777.355</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>10281.821</v>
+        <v>7922.982</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>10488.259</v>
+        <v>8111.325</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>9320.675999999999</v>
+        <v>6990.507</v>
       </c>
       <c r="J8" s="25" t="n">
         <v>738199552</v>
@@ -3409,139 +3210,139 @@
         <v>201326592</v>
       </c>
       <c r="L8" s="25" t="n">
+        <v>4194304</v>
+      </c>
+      <c r="M8" s="11" t="n">
+        <v>269.6485</v>
+      </c>
+      <c r="N8" s="11" t="n">
+        <v>95.4558</v>
+      </c>
+      <c r="O8" s="11" t="n">
+        <v>0.8988</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>4096-&gt;8192</t>
+        </is>
+      </c>
+      <c r="B9" s="52" t="n">
+        <v>262144</v>
+      </c>
+      <c r="C9" s="52" t="n">
+        <v>262144</v>
+      </c>
+      <c r="D9" s="53" t="n">
+        <v>1110.972</v>
+      </c>
+      <c r="E9" s="53" t="inlineStr"/>
+      <c r="F9" s="53" t="inlineStr"/>
+      <c r="G9" s="53" t="inlineStr"/>
+      <c r="H9" s="54" t="inlineStr"/>
+      <c r="I9" s="53" t="n">
+        <v>873.813</v>
+      </c>
+      <c r="J9" s="52" t="n">
+        <v>92274688</v>
+      </c>
+      <c r="K9" s="52" t="n">
+        <v>25165824</v>
+      </c>
+      <c r="L9" s="52" t="n">
+        <v>524288</v>
+      </c>
+      <c r="M9" s="53" t="n">
+        <v>235.9591</v>
+      </c>
+      <c r="N9" s="53" t="n">
+        <v>83.5295</v>
+      </c>
+      <c r="O9" s="53" t="n">
+        <v>0.7865</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>8192-&gt;16384</t>
+        </is>
+      </c>
+      <c r="B10" s="52" t="n">
+        <v>524288</v>
+      </c>
+      <c r="C10" s="52" t="n">
+        <v>524288</v>
+      </c>
+      <c r="D10" s="53" t="n">
+        <v>1771.152</v>
+      </c>
+      <c r="E10" s="53" t="inlineStr"/>
+      <c r="F10" s="53" t="inlineStr"/>
+      <c r="G10" s="53" t="inlineStr"/>
+      <c r="H10" s="54" t="inlineStr"/>
+      <c r="I10" s="53" t="n">
+        <v>1747.627</v>
+      </c>
+      <c r="J10" s="52" t="n">
+        <v>184549376</v>
+      </c>
+      <c r="K10" s="52" t="n">
+        <v>50331648</v>
+      </c>
+      <c r="L10" s="52" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="M10" s="53" t="n">
+        <v>296.0152</v>
+      </c>
+      <c r="N10" s="53" t="n">
+        <v>104.7894</v>
+      </c>
+      <c r="O10" s="53" t="n">
+        <v>0.9867</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>16384-&gt;32768</t>
+        </is>
+      </c>
+      <c r="B11" s="52" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="C11" s="52" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="D11" s="53" t="n">
+        <v>3505.376</v>
+      </c>
+      <c r="E11" s="53" t="inlineStr"/>
+      <c r="F11" s="53" t="inlineStr"/>
+      <c r="G11" s="53" t="inlineStr"/>
+      <c r="H11" s="54" t="inlineStr"/>
+      <c r="I11" s="53" t="n">
+        <v>3495.253</v>
+      </c>
+      <c r="J11" s="52" t="n">
+        <v>369098752</v>
+      </c>
+      <c r="K11" s="52" t="n">
+        <v>100663296</v>
+      </c>
+      <c r="L11" s="52" t="n">
         <v>2097152</v>
       </c>
-      <c r="M8" s="11" t="n">
-        <v>103.807</v>
-      </c>
-      <c r="N8" s="11" t="n">
-        <v>73.288</v>
-      </c>
-      <c r="O8" s="11" t="n">
-        <v>0.9227</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="44" t="inlineStr">
-        <is>
-          <t>2048-&gt;4096</t>
-        </is>
-      </c>
-      <c r="B9" s="45" t="n">
-        <v>262144</v>
-      </c>
-      <c r="C9" s="45" t="n">
-        <v>131072</v>
-      </c>
-      <c r="D9" s="46" t="n">
-        <v>1138.247</v>
-      </c>
-      <c r="E9" s="46" t="inlineStr"/>
-      <c r="F9" s="46" t="inlineStr"/>
-      <c r="G9" s="46" t="inlineStr"/>
-      <c r="H9" s="47" t="inlineStr"/>
-      <c r="I9" s="46" t="n">
-        <v>1165.084</v>
-      </c>
-      <c r="J9" s="45" t="n">
-        <v>92274688</v>
-      </c>
-      <c r="K9" s="45" t="n">
-        <v>25165824</v>
-      </c>
-      <c r="L9" s="45" t="n">
-        <v>262144</v>
-      </c>
-      <c r="M9" s="46" t="n">
-        <v>115.1525</v>
-      </c>
-      <c r="N9" s="46" t="n">
-        <v>81.29770000000001</v>
-      </c>
-      <c r="O9" s="46" t="n">
-        <v>1.0236</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="44" t="inlineStr">
-        <is>
-          <t>4096-&gt;8192</t>
-        </is>
-      </c>
-      <c r="B10" s="45" t="n">
-        <v>524288</v>
-      </c>
-      <c r="C10" s="45" t="n">
-        <v>262144</v>
-      </c>
-      <c r="D10" s="46" t="n">
-        <v>2375.837</v>
-      </c>
-      <c r="E10" s="46" t="inlineStr"/>
-      <c r="F10" s="46" t="inlineStr"/>
-      <c r="G10" s="46" t="inlineStr"/>
-      <c r="H10" s="47" t="inlineStr"/>
-      <c r="I10" s="46" t="n">
-        <v>2330.169</v>
-      </c>
-      <c r="J10" s="45" t="n">
-        <v>184549376</v>
-      </c>
-      <c r="K10" s="45" t="n">
-        <v>50331648</v>
-      </c>
-      <c r="L10" s="45" t="n">
-        <v>524288</v>
-      </c>
-      <c r="M10" s="46" t="n">
-        <v>110.3375</v>
-      </c>
-      <c r="N10" s="46" t="n">
-        <v>77.89830000000001</v>
-      </c>
-      <c r="O10" s="46" t="n">
-        <v>0.9808</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="44" t="inlineStr">
-        <is>
-          <t>8192-&gt;16384</t>
-        </is>
-      </c>
-      <c r="B11" s="45" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="C11" s="45" t="n">
-        <v>524288</v>
-      </c>
-      <c r="D11" s="46" t="n">
-        <v>4817.731</v>
-      </c>
-      <c r="E11" s="46" t="inlineStr"/>
-      <c r="F11" s="46" t="inlineStr"/>
-      <c r="G11" s="46" t="inlineStr"/>
-      <c r="H11" s="47" t="inlineStr"/>
-      <c r="I11" s="46" t="n">
-        <v>4660.338</v>
-      </c>
-      <c r="J11" s="45" t="n">
-        <v>369098752</v>
-      </c>
-      <c r="K11" s="45" t="n">
-        <v>100663296</v>
-      </c>
-      <c r="L11" s="45" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="M11" s="46" t="n">
-        <v>108.8247</v>
-      </c>
-      <c r="N11" s="46" t="n">
-        <v>76.8302</v>
-      </c>
-      <c r="O11" s="46" t="n">
-        <v>0.9673</v>
+      <c r="M11" s="53" t="n">
+        <v>299.1337</v>
+      </c>
+      <c r="N11" s="53" t="n">
+        <v>105.8933</v>
+      </c>
+      <c r="O11" s="53" t="n">
+        <v>0.9971</v>
       </c>
     </row>
     <row r="12">
@@ -3550,33 +3351,33 @@
           <t>FIT</t>
         </is>
       </c>
-      <c r="B12" s="48" t="inlineStr"/>
-      <c r="C12" s="48" t="inlineStr"/>
-      <c r="D12" s="49" t="n">
-        <v>541.932</v>
-      </c>
-      <c r="E12" s="50" t="n">
-        <v>0.00455068</v>
-      </c>
-      <c r="F12" s="51" t="n">
-        <v>0.99993</v>
-      </c>
-      <c r="G12" s="49" t="inlineStr"/>
-      <c r="H12" s="52" t="n">
+      <c r="B12" s="55" t="inlineStr"/>
+      <c r="C12" s="55" t="inlineStr"/>
+      <c r="D12" s="56" t="n">
+        <v>603.716</v>
+      </c>
+      <c r="E12" s="57" t="n">
+        <v>0.00343962</v>
+      </c>
+      <c r="F12" s="58" t="n">
+        <v>0.99882</v>
+      </c>
+      <c r="G12" s="56" t="inlineStr"/>
+      <c r="H12" s="59" t="n">
         <v>4</v>
       </c>
-      <c r="I12" s="49" t="inlineStr"/>
-      <c r="J12" s="48" t="inlineStr"/>
-      <c r="K12" s="48" t="inlineStr"/>
-      <c r="L12" s="48" t="inlineStr"/>
-      <c r="M12" s="49" t="n">
-        <v>109.8738</v>
-      </c>
-      <c r="N12" s="49" t="n">
-        <v>77.57089999999999</v>
-      </c>
-      <c r="O12" s="49" t="n">
-        <v>0.9767</v>
+      <c r="I12" s="56" t="inlineStr"/>
+      <c r="J12" s="55" t="inlineStr"/>
+      <c r="K12" s="55" t="inlineStr"/>
+      <c r="L12" s="55" t="inlineStr"/>
+      <c r="M12" s="56" t="n">
+        <v>290.7295</v>
+      </c>
+      <c r="N12" s="56" t="n">
+        <v>102.9182</v>
+      </c>
+      <c r="O12" s="56" t="n">
+        <v>0.9691</v>
       </c>
     </row>
   </sheetData>
@@ -3613,12 +3414,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>two2N sparsity 2:16 @ 225 MHz (pre-floorplan build)  -  source: sparse_2to16_225MHz.csv</t>
+          <t>two2N sparsity 2:32 @ 300 MHz (floorplanned build)  -  source: sparse_2to32_300MHz.csv</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="51" t="inlineStr">
         <is>
           <t>Rows 'a-&gt;b' are differentials between adjacent sizes (launch overhead cancels). Row 'FIT' is the least-squares fit: Best us = FIXED OVERHEAD, Mean us = slope in us/beat, Worst us = R^2.</t>
         </is>
@@ -3704,32 +3505,32 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>262144</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>262144</v>
+        <v>524288</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>1763.086</v>
+        <v>1498.933</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>1872.81</v>
+        <v>1629.342</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2043.634</v>
+        <v>1782.194</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>15.9</v>
+        <v>18.9</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>15</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>1165.084</v>
+        <v>873.813</v>
       </c>
       <c r="J5" s="25" t="n">
         <v>92276736</v>
@@ -3738,47 +3539,47 @@
         <v>25165824</v>
       </c>
       <c r="L5" s="25" t="n">
-        <v>524288</v>
+        <v>1048576</v>
       </c>
       <c r="M5" s="11" t="n">
-        <v>148.6847</v>
+        <v>349.7741</v>
       </c>
       <c r="N5" s="11" t="n">
-        <v>52.6356</v>
+        <v>62.2612</v>
       </c>
       <c r="O5" s="11" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.583</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>16384</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>524288</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>524288</v>
+        <v>1048576</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>2966.168</v>
+        <v>2570.294</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>3150.315</v>
+        <v>2629.207</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>3250.932</v>
+        <v>2690.06</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>9.6</v>
+        <v>4.7</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>15</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>2330.169</v>
+        <v>1747.627</v>
       </c>
       <c r="J6" s="25" t="n">
         <v>184551424</v>
@@ -3787,47 +3588,47 @@
         <v>50331648</v>
       </c>
       <c r="L6" s="25" t="n">
-        <v>1048576</v>
+        <v>2097152</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>176.756</v>
+        <v>407.9596</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>62.5723</v>
+        <v>72.6176</v>
       </c>
       <c r="O6" s="11" t="n">
-        <v>0.7856</v>
+        <v>0.6798999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>16384</t>
+          <t>32768</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1048576</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>1048576</v>
+        <v>2097152</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>5283.169</v>
+        <v>4369.453</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>5503.19</v>
+        <v>4435.333</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>5643.112</v>
+        <v>4530.465</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>6.8</v>
+        <v>3.7</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>15</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>4660.338</v>
+        <v>3495.253</v>
       </c>
       <c r="J7" s="25" t="n">
         <v>369100800</v>
@@ -3836,47 +3637,47 @@
         <v>100663296</v>
       </c>
       <c r="L7" s="25" t="n">
-        <v>2097152</v>
+        <v>4194304</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>198.4748</v>
+        <v>479.9576</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>70.26049999999999</v>
+        <v>85.4329</v>
       </c>
       <c r="O7" s="11" t="n">
-        <v>0.8821</v>
+        <v>0.7999000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>65536</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>2097152</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>2097152</v>
+        <v>4194304</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>10099.286</v>
+        <v>7905.593</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>10287.664</v>
+        <v>8047.452</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>10482.561</v>
+        <v>8193.317999999999</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>15</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>9320.675999999999</v>
+        <v>6990.507</v>
       </c>
       <c r="J8" s="25" t="n">
         <v>738199552</v>
@@ -3885,139 +3686,139 @@
         <v>201326592</v>
       </c>
       <c r="L8" s="25" t="n">
+        <v>8388608</v>
+      </c>
+      <c r="M8" s="11" t="n">
+        <v>530.5489</v>
+      </c>
+      <c r="N8" s="11" t="n">
+        <v>94.438</v>
+      </c>
+      <c r="O8" s="11" t="n">
+        <v>0.8842</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>8192-&gt;16384</t>
+        </is>
+      </c>
+      <c r="B9" s="52" t="n">
+        <v>262144</v>
+      </c>
+      <c r="C9" s="52" t="n">
+        <v>524288</v>
+      </c>
+      <c r="D9" s="53" t="n">
+        <v>1071.361</v>
+      </c>
+      <c r="E9" s="53" t="inlineStr"/>
+      <c r="F9" s="53" t="inlineStr"/>
+      <c r="G9" s="53" t="inlineStr"/>
+      <c r="H9" s="54" t="inlineStr"/>
+      <c r="I9" s="53" t="n">
+        <v>873.813</v>
+      </c>
+      <c r="J9" s="52" t="n">
+        <v>92274688</v>
+      </c>
+      <c r="K9" s="52" t="n">
+        <v>25165824</v>
+      </c>
+      <c r="L9" s="52" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="M9" s="53" t="n">
+        <v>489.3663</v>
+      </c>
+      <c r="N9" s="53" t="n">
+        <v>87.10720000000001</v>
+      </c>
+      <c r="O9" s="53" t="n">
+        <v>0.8156</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>16384-&gt;32768</t>
+        </is>
+      </c>
+      <c r="B10" s="52" t="n">
+        <v>524288</v>
+      </c>
+      <c r="C10" s="52" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="D10" s="53" t="n">
+        <v>1799.159</v>
+      </c>
+      <c r="E10" s="53" t="inlineStr"/>
+      <c r="F10" s="53" t="inlineStr"/>
+      <c r="G10" s="53" t="inlineStr"/>
+      <c r="H10" s="54" t="inlineStr"/>
+      <c r="I10" s="53" t="n">
+        <v>1747.627</v>
+      </c>
+      <c r="J10" s="52" t="n">
+        <v>184549376</v>
+      </c>
+      <c r="K10" s="52" t="n">
+        <v>50331648</v>
+      </c>
+      <c r="L10" s="52" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="M10" s="53" t="n">
+        <v>582.8145</v>
+      </c>
+      <c r="N10" s="53" t="n">
+        <v>103.741</v>
+      </c>
+      <c r="O10" s="53" t="n">
+        <v>0.9714</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>32768-&gt;65536</t>
+        </is>
+      </c>
+      <c r="B11" s="52" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="C11" s="52" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="D11" s="53" t="n">
+        <v>3536.14</v>
+      </c>
+      <c r="E11" s="53" t="inlineStr"/>
+      <c r="F11" s="53" t="inlineStr"/>
+      <c r="G11" s="53" t="inlineStr"/>
+      <c r="H11" s="54" t="inlineStr"/>
+      <c r="I11" s="53" t="n">
+        <v>3495.253</v>
+      </c>
+      <c r="J11" s="52" t="n">
+        <v>369098752</v>
+      </c>
+      <c r="K11" s="52" t="n">
+        <v>100663296</v>
+      </c>
+      <c r="L11" s="52" t="n">
         <v>4194304</v>
       </c>
-      <c r="M8" s="11" t="n">
-        <v>207.6535</v>
-      </c>
-      <c r="N8" s="11" t="n">
-        <v>73.5095</v>
-      </c>
-      <c r="O8" s="11" t="n">
-        <v>0.9229000000000001</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="44" t="inlineStr">
-        <is>
-          <t>4096-&gt;8192</t>
-        </is>
-      </c>
-      <c r="B9" s="45" t="n">
-        <v>262144</v>
-      </c>
-      <c r="C9" s="45" t="n">
-        <v>262144</v>
-      </c>
-      <c r="D9" s="46" t="n">
-        <v>1203.082</v>
-      </c>
-      <c r="E9" s="46" t="inlineStr"/>
-      <c r="F9" s="46" t="inlineStr"/>
-      <c r="G9" s="46" t="inlineStr"/>
-      <c r="H9" s="47" t="inlineStr"/>
-      <c r="I9" s="46" t="n">
-        <v>1165.084</v>
-      </c>
-      <c r="J9" s="45" t="n">
-        <v>92274688</v>
-      </c>
-      <c r="K9" s="45" t="n">
-        <v>25165824</v>
-      </c>
-      <c r="L9" s="45" t="n">
-        <v>524288</v>
-      </c>
-      <c r="M9" s="46" t="n">
-        <v>217.8937</v>
-      </c>
-      <c r="N9" s="46" t="n">
-        <v>77.1344</v>
-      </c>
-      <c r="O9" s="46" t="n">
-        <v>0.9684</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="44" t="inlineStr">
-        <is>
-          <t>8192-&gt;16384</t>
-        </is>
-      </c>
-      <c r="B10" s="45" t="n">
-        <v>524288</v>
-      </c>
-      <c r="C10" s="45" t="n">
-        <v>524288</v>
-      </c>
-      <c r="D10" s="46" t="n">
-        <v>2317.001</v>
-      </c>
-      <c r="E10" s="46" t="inlineStr"/>
-      <c r="F10" s="46" t="inlineStr"/>
-      <c r="G10" s="46" t="inlineStr"/>
-      <c r="H10" s="47" t="inlineStr"/>
-      <c r="I10" s="46" t="n">
-        <v>2330.169</v>
-      </c>
-      <c r="J10" s="45" t="n">
-        <v>184549376</v>
-      </c>
-      <c r="K10" s="45" t="n">
-        <v>50331648</v>
-      </c>
-      <c r="L10" s="45" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="M10" s="46" t="n">
-        <v>226.2787</v>
-      </c>
-      <c r="N10" s="46" t="n">
-        <v>80.1027</v>
-      </c>
-      <c r="O10" s="46" t="n">
-        <v>1.0057</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="44" t="inlineStr">
-        <is>
-          <t>16384-&gt;32768</t>
-        </is>
-      </c>
-      <c r="B11" s="45" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="C11" s="45" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="D11" s="46" t="n">
-        <v>4816.117</v>
-      </c>
-      <c r="E11" s="46" t="inlineStr"/>
-      <c r="F11" s="46" t="inlineStr"/>
-      <c r="G11" s="46" t="inlineStr"/>
-      <c r="H11" s="47" t="inlineStr"/>
-      <c r="I11" s="46" t="n">
-        <v>4660.338</v>
-      </c>
-      <c r="J11" s="45" t="n">
-        <v>369098752</v>
-      </c>
-      <c r="K11" s="45" t="n">
-        <v>100663296</v>
-      </c>
-      <c r="L11" s="45" t="n">
-        <v>2097152</v>
-      </c>
-      <c r="M11" s="46" t="n">
-        <v>217.7223</v>
-      </c>
-      <c r="N11" s="46" t="n">
-        <v>77.0737</v>
-      </c>
-      <c r="O11" s="46" t="n">
-        <v>0.9677</v>
+      <c r="M11" s="53" t="n">
+        <v>593.0625</v>
+      </c>
+      <c r="N11" s="53" t="n">
+        <v>105.5651</v>
+      </c>
+      <c r="O11" s="53" t="n">
+        <v>0.9883999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -4026,33 +3827,33 @@
           <t>FIT</t>
         </is>
       </c>
-      <c r="B12" s="48" t="inlineStr"/>
-      <c r="C12" s="48" t="inlineStr"/>
-      <c r="D12" s="49" t="n">
-        <v>566.604</v>
-      </c>
-      <c r="E12" s="50" t="n">
-        <v>0.00453829</v>
-      </c>
-      <c r="F12" s="51" t="n">
-        <v>0.9999400000000001</v>
-      </c>
-      <c r="G12" s="49" t="inlineStr"/>
-      <c r="H12" s="52" t="n">
+      <c r="B12" s="55" t="inlineStr"/>
+      <c r="C12" s="55" t="inlineStr"/>
+      <c r="D12" s="56" t="n">
+        <v>685.496</v>
+      </c>
+      <c r="E12" s="57" t="n">
+        <v>0.00345924</v>
+      </c>
+      <c r="F12" s="58" t="n">
+        <v>0.99923</v>
+      </c>
+      <c r="G12" s="56" t="inlineStr"/>
+      <c r="H12" s="59" t="n">
         <v>4</v>
       </c>
-      <c r="I12" s="49" t="inlineStr"/>
-      <c r="J12" s="48" t="inlineStr"/>
-      <c r="K12" s="48" t="inlineStr"/>
-      <c r="L12" s="48" t="inlineStr"/>
-      <c r="M12" s="49" t="n">
-        <v>220.3472</v>
-      </c>
-      <c r="N12" s="49" t="n">
-        <v>78.0029</v>
-      </c>
-      <c r="O12" s="49" t="n">
-        <v>0.9792999999999999</v>
+      <c r="I12" s="56" t="inlineStr"/>
+      <c r="J12" s="55" t="inlineStr"/>
+      <c r="K12" s="55" t="inlineStr"/>
+      <c r="L12" s="55" t="inlineStr"/>
+      <c r="M12" s="56" t="n">
+        <v>578.1615</v>
+      </c>
+      <c r="N12" s="56" t="n">
+        <v>102.9128</v>
+      </c>
+      <c r="O12" s="56" t="n">
+        <v>0.9636</v>
       </c>
     </row>
   </sheetData>
@@ -4089,12 +3890,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>two2N sparsity 2:32 @ 225 MHz (pre-floorplan build)  -  source: sparse_2to32_225MHz.csv</t>
+          <t>two2N sparsity 2:4 @ 225 MHz (pre-floorplan build)  -  source: sparse_2to4_225MHz.csv</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="51" t="inlineStr">
         <is>
           <t>Rows 'a-&gt;b' are differentials between adjacent sizes (launch overhead cancels). Row 'FIT' is the least-squares fit: Best us = FIXED OVERHEAD, Mean us = slope in us/beat, Worst us = R^2.</t>
         </is>
@@ -4180,13 +3981,1441 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>262144</v>
       </c>
       <c r="C5" s="25" t="n">
+        <v>65536</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>1744.379</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>1844.359</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>2130.395</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>1165.084</v>
+      </c>
+      <c r="J5" s="25" t="n">
+        <v>92276736</v>
+      </c>
+      <c r="K5" s="25" t="n">
+        <v>25165824</v>
+      </c>
+      <c r="L5" s="25" t="n">
+        <v>131072</v>
+      </c>
+      <c r="M5" s="11" t="n">
+        <v>37.5698</v>
+      </c>
+      <c r="N5" s="11" t="n">
+        <v>52.9746</v>
+      </c>
+      <c r="O5" s="11" t="n">
+        <v>0.6679</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="n">
+        <v>524288</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>131072</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>3023.539</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>3141.519</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>3292.324</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>2330.169</v>
+      </c>
+      <c r="J6" s="25" t="n">
+        <v>184551424</v>
+      </c>
+      <c r="K6" s="25" t="n">
+        <v>50331648</v>
+      </c>
+      <c r="L6" s="25" t="n">
+        <v>262144</v>
+      </c>
+      <c r="M6" s="11" t="n">
+        <v>43.3505</v>
+      </c>
+      <c r="N6" s="11" t="n">
+        <v>61.1249</v>
+      </c>
+      <c r="O6" s="11" t="n">
+        <v>0.7707000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>4096</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>262144</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>5240.044</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>5444.641</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>5715.295</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>4660.338</v>
+      </c>
+      <c r="J7" s="25" t="n">
+        <v>369100800</v>
+      </c>
+      <c r="K7" s="25" t="n">
+        <v>100663296</v>
+      </c>
+      <c r="L7" s="25" t="n">
+        <v>524288</v>
+      </c>
+      <c r="M7" s="11" t="n">
+        <v>50.0271</v>
+      </c>
+      <c r="N7" s="11" t="n">
+        <v>70.5385</v>
+      </c>
+      <c r="O7" s="11" t="n">
+        <v>0.8894</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>8192</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>524288</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>9977.441999999999</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>10139.83</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>10300.308</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>9320.675999999999</v>
+      </c>
+      <c r="J8" s="25" t="n">
+        <v>738199552</v>
+      </c>
+      <c r="K8" s="25" t="n">
+        <v>201326592</v>
+      </c>
+      <c r="L8" s="25" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="M8" s="11" t="n">
+        <v>52.5473</v>
+      </c>
+      <c r="N8" s="11" t="n">
+        <v>74.0919</v>
+      </c>
+      <c r="O8" s="11" t="n">
+        <v>0.9342</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>1024-&gt;2048</t>
+        </is>
+      </c>
+      <c r="B9" s="52" t="n">
+        <v>262144</v>
+      </c>
+      <c r="C9" s="52" t="n">
+        <v>65536</v>
+      </c>
+      <c r="D9" s="53" t="n">
+        <v>1279.16</v>
+      </c>
+      <c r="E9" s="53" t="inlineStr"/>
+      <c r="F9" s="53" t="inlineStr"/>
+      <c r="G9" s="53" t="inlineStr"/>
+      <c r="H9" s="54" t="inlineStr"/>
+      <c r="I9" s="53" t="n">
+        <v>1165.084</v>
+      </c>
+      <c r="J9" s="52" t="n">
+        <v>92274688</v>
+      </c>
+      <c r="K9" s="52" t="n">
+        <v>25165824</v>
+      </c>
+      <c r="L9" s="52" t="n">
+        <v>131072</v>
+      </c>
+      <c r="M9" s="53" t="n">
+        <v>51.2336</v>
+      </c>
+      <c r="N9" s="53" t="n">
+        <v>72.2394</v>
+      </c>
+      <c r="O9" s="53" t="n">
+        <v>0.9108000000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>2048-&gt;4096</t>
+        </is>
+      </c>
+      <c r="B10" s="52" t="n">
+        <v>524288</v>
+      </c>
+      <c r="C10" s="52" t="n">
+        <v>131072</v>
+      </c>
+      <c r="D10" s="53" t="n">
+        <v>2216.505</v>
+      </c>
+      <c r="E10" s="53" t="inlineStr"/>
+      <c r="F10" s="53" t="inlineStr"/>
+      <c r="G10" s="53" t="inlineStr"/>
+      <c r="H10" s="54" t="inlineStr"/>
+      <c r="I10" s="53" t="n">
+        <v>2330.169</v>
+      </c>
+      <c r="J10" s="52" t="n">
+        <v>184549376</v>
+      </c>
+      <c r="K10" s="52" t="n">
+        <v>50331648</v>
+      </c>
+      <c r="L10" s="52" t="n">
+        <v>262144</v>
+      </c>
+      <c r="M10" s="53" t="n">
+        <v>59.1345</v>
+      </c>
+      <c r="N10" s="53" t="n">
+        <v>83.3797</v>
+      </c>
+      <c r="O10" s="53" t="n">
+        <v>1.0513</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>4096-&gt;8192</t>
+        </is>
+      </c>
+      <c r="B11" s="52" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="C11" s="52" t="n">
+        <v>262144</v>
+      </c>
+      <c r="D11" s="53" t="n">
+        <v>4737.398</v>
+      </c>
+      <c r="E11" s="53" t="inlineStr"/>
+      <c r="F11" s="53" t="inlineStr"/>
+      <c r="G11" s="53" t="inlineStr"/>
+      <c r="H11" s="54" t="inlineStr"/>
+      <c r="I11" s="53" t="n">
+        <v>4660.338</v>
+      </c>
+      <c r="J11" s="52" t="n">
+        <v>369098752</v>
+      </c>
+      <c r="K11" s="52" t="n">
+        <v>100663296</v>
+      </c>
+      <c r="L11" s="52" t="n">
+        <v>524288</v>
+      </c>
+      <c r="M11" s="53" t="n">
+        <v>55.335</v>
+      </c>
+      <c r="N11" s="53" t="n">
+        <v>78.0224</v>
+      </c>
+      <c r="O11" s="53" t="n">
+        <v>0.9837</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>FIT</t>
+        </is>
+      </c>
+      <c r="B12" s="55" t="inlineStr"/>
+      <c r="C12" s="55" t="inlineStr"/>
+      <c r="D12" s="56" t="n">
+        <v>610.364</v>
+      </c>
+      <c r="E12" s="57" t="n">
+        <v>0.00446166</v>
+      </c>
+      <c r="F12" s="58" t="n">
+        <v>0.99977</v>
+      </c>
+      <c r="G12" s="56" t="inlineStr"/>
+      <c r="H12" s="59" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="56" t="inlineStr"/>
+      <c r="J12" s="55" t="inlineStr"/>
+      <c r="K12" s="55" t="inlineStr"/>
+      <c r="L12" s="55" t="inlineStr"/>
+      <c r="M12" s="56" t="n">
+        <v>56.033</v>
+      </c>
+      <c r="N12" s="56" t="n">
+        <v>79.0065</v>
+      </c>
+      <c r="O12" s="56" t="n">
+        <v>0.9961</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>two2N sparsity 2:8 @ 225 MHz (pre-floorplan build)  -  source: sparse_2to8_225MHz.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="51" t="inlineStr">
+        <is>
+          <t>Rows 'a-&gt;b' are differentials between adjacent sizes (launch overhead cancels). Row 'FIT' is the least-squares fit: Best us = FIXED OVERHEAD, Mean us = slope in us/beat, Worst us = R^2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Size / pair</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Weight beats</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Best us</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Mean us</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Worst us</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Spread %</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Reps</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Ideal us</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Bytes in</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>of which index</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Bytes out</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>Mrow/s</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>GB/s</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>beats/cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="n">
+        <v>262144</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>131072</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>1769.391</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>1871.982</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>2012.449</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>1165.084</v>
+      </c>
+      <c r="J5" s="25" t="n">
+        <v>92276736</v>
+      </c>
+      <c r="K5" s="25" t="n">
+        <v>25165824</v>
+      </c>
+      <c r="L5" s="25" t="n">
+        <v>262144</v>
+      </c>
+      <c r="M5" s="11" t="n">
+        <v>74.0775</v>
+      </c>
+      <c r="N5" s="11" t="n">
+        <v>52.2998</v>
+      </c>
+      <c r="O5" s="11" t="n">
+        <v>0.6585</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>4096</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="n">
+        <v>524288</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>262144</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>2907.638</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>3105.124</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>3211.361</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>2330.169</v>
+      </c>
+      <c r="J6" s="25" t="n">
+        <v>184551424</v>
+      </c>
+      <c r="K6" s="25" t="n">
+        <v>50331648</v>
+      </c>
+      <c r="L6" s="25" t="n">
+        <v>524288</v>
+      </c>
+      <c r="M6" s="11" t="n">
+        <v>90.157</v>
+      </c>
+      <c r="N6" s="11" t="n">
+        <v>63.6516</v>
+      </c>
+      <c r="O6" s="11" t="n">
+        <v>0.8014</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>8192</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>524288</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>5283.475</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>5517.496</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>5732.823</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>4660.338</v>
+      </c>
+      <c r="J7" s="25" t="n">
+        <v>369100800</v>
+      </c>
+      <c r="K7" s="25" t="n">
+        <v>100663296</v>
+      </c>
+      <c r="L7" s="25" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="M7" s="11" t="n">
+        <v>99.2317</v>
+      </c>
+      <c r="N7" s="11" t="n">
+        <v>70.0579</v>
+      </c>
+      <c r="O7" s="11" t="n">
+        <v>0.8821</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>16384</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>10101.206</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>10281.821</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>10488.259</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>9320.675999999999</v>
+      </c>
+      <c r="J8" s="25" t="n">
+        <v>738199552</v>
+      </c>
+      <c r="K8" s="25" t="n">
+        <v>201326592</v>
+      </c>
+      <c r="L8" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="M8" s="11" t="n">
+        <v>103.807</v>
+      </c>
+      <c r="N8" s="11" t="n">
+        <v>73.288</v>
+      </c>
+      <c r="O8" s="11" t="n">
+        <v>0.9227</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>2048-&gt;4096</t>
+        </is>
+      </c>
+      <c r="B9" s="52" t="n">
+        <v>262144</v>
+      </c>
+      <c r="C9" s="52" t="n">
+        <v>131072</v>
+      </c>
+      <c r="D9" s="53" t="n">
+        <v>1138.247</v>
+      </c>
+      <c r="E9" s="53" t="inlineStr"/>
+      <c r="F9" s="53" t="inlineStr"/>
+      <c r="G9" s="53" t="inlineStr"/>
+      <c r="H9" s="54" t="inlineStr"/>
+      <c r="I9" s="53" t="n">
+        <v>1165.084</v>
+      </c>
+      <c r="J9" s="52" t="n">
+        <v>92274688</v>
+      </c>
+      <c r="K9" s="52" t="n">
+        <v>25165824</v>
+      </c>
+      <c r="L9" s="52" t="n">
+        <v>262144</v>
+      </c>
+      <c r="M9" s="53" t="n">
+        <v>115.1525</v>
+      </c>
+      <c r="N9" s="53" t="n">
+        <v>81.29770000000001</v>
+      </c>
+      <c r="O9" s="53" t="n">
+        <v>1.0236</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>4096-&gt;8192</t>
+        </is>
+      </c>
+      <c r="B10" s="52" t="n">
+        <v>524288</v>
+      </c>
+      <c r="C10" s="52" t="n">
+        <v>262144</v>
+      </c>
+      <c r="D10" s="53" t="n">
+        <v>2375.837</v>
+      </c>
+      <c r="E10" s="53" t="inlineStr"/>
+      <c r="F10" s="53" t="inlineStr"/>
+      <c r="G10" s="53" t="inlineStr"/>
+      <c r="H10" s="54" t="inlineStr"/>
+      <c r="I10" s="53" t="n">
+        <v>2330.169</v>
+      </c>
+      <c r="J10" s="52" t="n">
+        <v>184549376</v>
+      </c>
+      <c r="K10" s="52" t="n">
+        <v>50331648</v>
+      </c>
+      <c r="L10" s="52" t="n">
+        <v>524288</v>
+      </c>
+      <c r="M10" s="53" t="n">
+        <v>110.3375</v>
+      </c>
+      <c r="N10" s="53" t="n">
+        <v>77.89830000000001</v>
+      </c>
+      <c r="O10" s="53" t="n">
+        <v>0.9808</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>8192-&gt;16384</t>
+        </is>
+      </c>
+      <c r="B11" s="52" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="C11" s="52" t="n">
+        <v>524288</v>
+      </c>
+      <c r="D11" s="53" t="n">
+        <v>4817.731</v>
+      </c>
+      <c r="E11" s="53" t="inlineStr"/>
+      <c r="F11" s="53" t="inlineStr"/>
+      <c r="G11" s="53" t="inlineStr"/>
+      <c r="H11" s="54" t="inlineStr"/>
+      <c r="I11" s="53" t="n">
+        <v>4660.338</v>
+      </c>
+      <c r="J11" s="52" t="n">
+        <v>369098752</v>
+      </c>
+      <c r="K11" s="52" t="n">
+        <v>100663296</v>
+      </c>
+      <c r="L11" s="52" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="M11" s="53" t="n">
+        <v>108.8247</v>
+      </c>
+      <c r="N11" s="53" t="n">
+        <v>76.8302</v>
+      </c>
+      <c r="O11" s="53" t="n">
+        <v>0.9673</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>FIT</t>
+        </is>
+      </c>
+      <c r="B12" s="55" t="inlineStr"/>
+      <c r="C12" s="55" t="inlineStr"/>
+      <c r="D12" s="56" t="n">
+        <v>541.932</v>
+      </c>
+      <c r="E12" s="57" t="n">
+        <v>0.00455068</v>
+      </c>
+      <c r="F12" s="58" t="n">
+        <v>0.99993</v>
+      </c>
+      <c r="G12" s="56" t="inlineStr"/>
+      <c r="H12" s="59" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="56" t="inlineStr"/>
+      <c r="J12" s="55" t="inlineStr"/>
+      <c r="K12" s="55" t="inlineStr"/>
+      <c r="L12" s="55" t="inlineStr"/>
+      <c r="M12" s="56" t="n">
+        <v>109.8738</v>
+      </c>
+      <c r="N12" s="56" t="n">
+        <v>77.57089999999999</v>
+      </c>
+      <c r="O12" s="56" t="n">
+        <v>0.9767</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>two2N sparsity 2:16 @ 225 MHz (pre-floorplan build)  -  source: sparse_2to16_225MHz.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="51" t="inlineStr">
+        <is>
+          <t>Rows 'a-&gt;b' are differentials between adjacent sizes (launch overhead cancels). Row 'FIT' is the least-squares fit: Best us = FIXED OVERHEAD, Mean us = slope in us/beat, Worst us = R^2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Size / pair</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Weight beats</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Best us</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Mean us</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Worst us</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Spread %</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Reps</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Ideal us</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Bytes in</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>of which index</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Bytes out</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>Mrow/s</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>GB/s</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>beats/cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>4096</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="n">
+        <v>262144</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>262144</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>1763.086</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>1872.81</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>2043.634</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>1165.084</v>
+      </c>
+      <c r="J5" s="25" t="n">
+        <v>92276736</v>
+      </c>
+      <c r="K5" s="25" t="n">
+        <v>25165824</v>
+      </c>
+      <c r="L5" s="25" t="n">
+        <v>524288</v>
+      </c>
+      <c r="M5" s="11" t="n">
+        <v>148.6847</v>
+      </c>
+      <c r="N5" s="11" t="n">
+        <v>52.6356</v>
+      </c>
+      <c r="O5" s="11" t="n">
+        <v>0.6608000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>8192</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="n">
+        <v>524288</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>524288</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>2966.168</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>3150.315</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>3250.932</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>2330.169</v>
+      </c>
+      <c r="J6" s="25" t="n">
+        <v>184551424</v>
+      </c>
+      <c r="K6" s="25" t="n">
+        <v>50331648</v>
+      </c>
+      <c r="L6" s="25" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="M6" s="11" t="n">
+        <v>176.756</v>
+      </c>
+      <c r="N6" s="11" t="n">
+        <v>62.5723</v>
+      </c>
+      <c r="O6" s="11" t="n">
+        <v>0.7856</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>16384</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>5283.169</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>5503.19</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>5643.112</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>4660.338</v>
+      </c>
+      <c r="J7" s="25" t="n">
+        <v>369100800</v>
+      </c>
+      <c r="K7" s="25" t="n">
+        <v>100663296</v>
+      </c>
+      <c r="L7" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="M7" s="11" t="n">
+        <v>198.4748</v>
+      </c>
+      <c r="N7" s="11" t="n">
+        <v>70.26049999999999</v>
+      </c>
+      <c r="O7" s="11" t="n">
+        <v>0.8821</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>32768</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>10099.286</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>10287.664</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>10482.561</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>9320.675999999999</v>
+      </c>
+      <c r="J8" s="25" t="n">
+        <v>738199552</v>
+      </c>
+      <c r="K8" s="25" t="n">
+        <v>201326592</v>
+      </c>
+      <c r="L8" s="25" t="n">
+        <v>4194304</v>
+      </c>
+      <c r="M8" s="11" t="n">
+        <v>207.6535</v>
+      </c>
+      <c r="N8" s="11" t="n">
+        <v>73.5095</v>
+      </c>
+      <c r="O8" s="11" t="n">
+        <v>0.9229000000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>4096-&gt;8192</t>
+        </is>
+      </c>
+      <c r="B9" s="52" t="n">
+        <v>262144</v>
+      </c>
+      <c r="C9" s="52" t="n">
+        <v>262144</v>
+      </c>
+      <c r="D9" s="53" t="n">
+        <v>1203.082</v>
+      </c>
+      <c r="E9" s="53" t="inlineStr"/>
+      <c r="F9" s="53" t="inlineStr"/>
+      <c r="G9" s="53" t="inlineStr"/>
+      <c r="H9" s="54" t="inlineStr"/>
+      <c r="I9" s="53" t="n">
+        <v>1165.084</v>
+      </c>
+      <c r="J9" s="52" t="n">
+        <v>92274688</v>
+      </c>
+      <c r="K9" s="52" t="n">
+        <v>25165824</v>
+      </c>
+      <c r="L9" s="52" t="n">
+        <v>524288</v>
+      </c>
+      <c r="M9" s="53" t="n">
+        <v>217.8937</v>
+      </c>
+      <c r="N9" s="53" t="n">
+        <v>77.1344</v>
+      </c>
+      <c r="O9" s="53" t="n">
+        <v>0.9684</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>8192-&gt;16384</t>
+        </is>
+      </c>
+      <c r="B10" s="52" t="n">
+        <v>524288</v>
+      </c>
+      <c r="C10" s="52" t="n">
+        <v>524288</v>
+      </c>
+      <c r="D10" s="53" t="n">
+        <v>2317.001</v>
+      </c>
+      <c r="E10" s="53" t="inlineStr"/>
+      <c r="F10" s="53" t="inlineStr"/>
+      <c r="G10" s="53" t="inlineStr"/>
+      <c r="H10" s="54" t="inlineStr"/>
+      <c r="I10" s="53" t="n">
+        <v>2330.169</v>
+      </c>
+      <c r="J10" s="52" t="n">
+        <v>184549376</v>
+      </c>
+      <c r="K10" s="52" t="n">
+        <v>50331648</v>
+      </c>
+      <c r="L10" s="52" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="M10" s="53" t="n">
+        <v>226.2787</v>
+      </c>
+      <c r="N10" s="53" t="n">
+        <v>80.1027</v>
+      </c>
+      <c r="O10" s="53" t="n">
+        <v>1.0057</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>16384-&gt;32768</t>
+        </is>
+      </c>
+      <c r="B11" s="52" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="C11" s="52" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="D11" s="53" t="n">
+        <v>4816.117</v>
+      </c>
+      <c r="E11" s="53" t="inlineStr"/>
+      <c r="F11" s="53" t="inlineStr"/>
+      <c r="G11" s="53" t="inlineStr"/>
+      <c r="H11" s="54" t="inlineStr"/>
+      <c r="I11" s="53" t="n">
+        <v>4660.338</v>
+      </c>
+      <c r="J11" s="52" t="n">
+        <v>369098752</v>
+      </c>
+      <c r="K11" s="52" t="n">
+        <v>100663296</v>
+      </c>
+      <c r="L11" s="52" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="M11" s="53" t="n">
+        <v>217.7223</v>
+      </c>
+      <c r="N11" s="53" t="n">
+        <v>77.0737</v>
+      </c>
+      <c r="O11" s="53" t="n">
+        <v>0.9677</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>FIT</t>
+        </is>
+      </c>
+      <c r="B12" s="55" t="inlineStr"/>
+      <c r="C12" s="55" t="inlineStr"/>
+      <c r="D12" s="56" t="n">
+        <v>566.604</v>
+      </c>
+      <c r="E12" s="57" t="n">
+        <v>0.00453829</v>
+      </c>
+      <c r="F12" s="58" t="n">
+        <v>0.9999400000000001</v>
+      </c>
+      <c r="G12" s="56" t="inlineStr"/>
+      <c r="H12" s="59" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="56" t="inlineStr"/>
+      <c r="J12" s="55" t="inlineStr"/>
+      <c r="K12" s="55" t="inlineStr"/>
+      <c r="L12" s="55" t="inlineStr"/>
+      <c r="M12" s="56" t="n">
+        <v>220.3472</v>
+      </c>
+      <c r="N12" s="56" t="n">
+        <v>78.0029</v>
+      </c>
+      <c r="O12" s="56" t="n">
+        <v>0.9792999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>two2N sparsity 2:32 @ 225 MHz (pre-floorplan build)  -  source: sparse_2to32_225MHz.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="51" t="inlineStr">
+        <is>
+          <t>Rows 'a-&gt;b' are differentials between adjacent sizes (launch overhead cancels). Row 'FIT' is the least-squares fit: Best us = FIXED OVERHEAD, Mean us = slope in us/beat, Worst us = R^2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Size / pair</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Weight beats</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Best us</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Mean us</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Worst us</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Spread %</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Reps</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Ideal us</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Bytes in</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>of which index</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Bytes out</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>Mrow/s</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>GB/s</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>beats/cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>8192</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="n">
+        <v>262144</v>
+      </c>
+      <c r="C5" s="25" t="n">
         <v>524288</v>
       </c>
       <c r="D5" s="11" t="n">
@@ -4374,125 +5603,125 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="44" t="inlineStr">
+      <c r="A9" s="43" t="inlineStr">
         <is>
           <t>8192-&gt;16384</t>
         </is>
       </c>
-      <c r="B9" s="45" t="n">
+      <c r="B9" s="52" t="n">
         <v>262144</v>
       </c>
-      <c r="C9" s="45" t="n">
+      <c r="C9" s="52" t="n">
         <v>524288</v>
       </c>
-      <c r="D9" s="46" t="n">
+      <c r="D9" s="53" t="n">
         <v>1209.366</v>
       </c>
-      <c r="E9" s="46" t="inlineStr"/>
-      <c r="F9" s="46" t="inlineStr"/>
-      <c r="G9" s="46" t="inlineStr"/>
-      <c r="H9" s="47" t="inlineStr"/>
-      <c r="I9" s="46" t="n">
+      <c r="E9" s="53" t="inlineStr"/>
+      <c r="F9" s="53" t="inlineStr"/>
+      <c r="G9" s="53" t="inlineStr"/>
+      <c r="H9" s="54" t="inlineStr"/>
+      <c r="I9" s="53" t="n">
         <v>1165.084</v>
       </c>
-      <c r="J9" s="45" t="n">
+      <c r="J9" s="52" t="n">
         <v>92274688</v>
       </c>
-      <c r="K9" s="45" t="n">
+      <c r="K9" s="52" t="n">
         <v>25165824</v>
       </c>
-      <c r="L9" s="45" t="n">
+      <c r="L9" s="52" t="n">
         <v>1048576</v>
       </c>
-      <c r="M9" s="46" t="n">
+      <c r="M9" s="53" t="n">
         <v>433.523</v>
       </c>
-      <c r="N9" s="46" t="n">
+      <c r="N9" s="53" t="n">
         <v>77.1671</v>
       </c>
-      <c r="O9" s="46" t="n">
+      <c r="O9" s="53" t="n">
         <v>0.9634</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="44" t="inlineStr">
+      <c r="A10" s="43" t="inlineStr">
         <is>
           <t>16384-&gt;32768</t>
         </is>
       </c>
-      <c r="B10" s="45" t="n">
+      <c r="B10" s="52" t="n">
         <v>524288</v>
       </c>
-      <c r="C10" s="45" t="n">
+      <c r="C10" s="52" t="n">
         <v>1048576</v>
       </c>
-      <c r="D10" s="46" t="n">
+      <c r="D10" s="53" t="n">
         <v>2394.994</v>
       </c>
-      <c r="E10" s="46" t="inlineStr"/>
-      <c r="F10" s="46" t="inlineStr"/>
-      <c r="G10" s="46" t="inlineStr"/>
-      <c r="H10" s="47" t="inlineStr"/>
-      <c r="I10" s="46" t="n">
+      <c r="E10" s="53" t="inlineStr"/>
+      <c r="F10" s="53" t="inlineStr"/>
+      <c r="G10" s="53" t="inlineStr"/>
+      <c r="H10" s="54" t="inlineStr"/>
+      <c r="I10" s="53" t="n">
         <v>2330.169</v>
       </c>
-      <c r="J10" s="45" t="n">
+      <c r="J10" s="52" t="n">
         <v>184549376</v>
       </c>
-      <c r="K10" s="45" t="n">
+      <c r="K10" s="52" t="n">
         <v>50331648</v>
       </c>
-      <c r="L10" s="45" t="n">
+      <c r="L10" s="52" t="n">
         <v>2097152</v>
       </c>
-      <c r="M10" s="46" t="n">
+      <c r="M10" s="53" t="n">
         <v>437.8199</v>
       </c>
-      <c r="N10" s="46" t="n">
+      <c r="N10" s="53" t="n">
         <v>77.9319</v>
       </c>
-      <c r="O10" s="46" t="n">
+      <c r="O10" s="53" t="n">
         <v>0.9729</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="44" t="inlineStr">
+      <c r="A11" s="43" t="inlineStr">
         <is>
           <t>32768-&gt;65536</t>
         </is>
       </c>
-      <c r="B11" s="45" t="n">
+      <c r="B11" s="52" t="n">
         <v>1048576</v>
       </c>
-      <c r="C11" s="45" t="n">
+      <c r="C11" s="52" t="n">
         <v>2097152</v>
       </c>
-      <c r="D11" s="46" t="n">
+      <c r="D11" s="53" t="n">
         <v>4907.979</v>
       </c>
-      <c r="E11" s="46" t="inlineStr"/>
-      <c r="F11" s="46" t="inlineStr"/>
-      <c r="G11" s="46" t="inlineStr"/>
-      <c r="H11" s="47" t="inlineStr"/>
-      <c r="I11" s="46" t="n">
+      <c r="E11" s="53" t="inlineStr"/>
+      <c r="F11" s="53" t="inlineStr"/>
+      <c r="G11" s="53" t="inlineStr"/>
+      <c r="H11" s="54" t="inlineStr"/>
+      <c r="I11" s="53" t="n">
         <v>4660.338</v>
       </c>
-      <c r="J11" s="45" t="n">
+      <c r="J11" s="52" t="n">
         <v>369098752</v>
       </c>
-      <c r="K11" s="45" t="n">
+      <c r="K11" s="52" t="n">
         <v>100663296</v>
       </c>
-      <c r="L11" s="45" t="n">
+      <c r="L11" s="52" t="n">
         <v>4194304</v>
       </c>
-      <c r="M11" s="46" t="n">
+      <c r="M11" s="53" t="n">
         <v>427.2944</v>
       </c>
-      <c r="N11" s="46" t="n">
+      <c r="N11" s="53" t="n">
         <v>76.05840000000001</v>
       </c>
-      <c r="O11" s="46" t="n">
+      <c r="O11" s="53" t="n">
         <v>0.9495</v>
       </c>
     </row>
@@ -4502,32 +5731,32 @@
           <t>FIT</t>
         </is>
       </c>
-      <c r="B12" s="48" t="inlineStr"/>
-      <c r="C12" s="48" t="inlineStr"/>
-      <c r="D12" s="49" t="n">
+      <c r="B12" s="55" t="inlineStr"/>
+      <c r="C12" s="55" t="inlineStr"/>
+      <c r="D12" s="56" t="n">
         <v>490.176</v>
       </c>
-      <c r="E12" s="50" t="n">
+      <c r="E12" s="57" t="n">
         <v>0.00463896</v>
       </c>
-      <c r="F12" s="51" t="n">
+      <c r="F12" s="58" t="n">
         <v>0.99997</v>
       </c>
-      <c r="G12" s="49" t="inlineStr"/>
-      <c r="H12" s="52" t="n">
+      <c r="G12" s="56" t="inlineStr"/>
+      <c r="H12" s="59" t="n">
         <v>4</v>
       </c>
-      <c r="I12" s="49" t="inlineStr"/>
-      <c r="J12" s="48" t="inlineStr"/>
-      <c r="K12" s="48" t="inlineStr"/>
-      <c r="L12" s="48" t="inlineStr"/>
-      <c r="M12" s="49" t="n">
+      <c r="I12" s="56" t="inlineStr"/>
+      <c r="J12" s="55" t="inlineStr"/>
+      <c r="K12" s="55" t="inlineStr"/>
+      <c r="L12" s="55" t="inlineStr"/>
+      <c r="M12" s="56" t="n">
         <v>431.1315</v>
       </c>
-      <c r="N12" s="49" t="n">
+      <c r="N12" s="56" t="n">
         <v>76.7414</v>
       </c>
-      <c r="O12" s="49" t="n">
+      <c r="O12" s="56" t="n">
         <v>0.9581</v>
       </c>
     </row>
@@ -7645,275 +8874,562 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A42"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="118" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="41" t="inlineStr">
-        <is>
-          <t>GEMV hardware measurement - method and caveats</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="24" t="inlineStr"/>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="42" t="inlineStr">
-        <is>
-          <t>PLATFORM</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44" customHeight="1">
-      <c r="A4" s="24" t="inlineStr">
-        <is>
-          <t>Alveo U280 (xcu280-fsvh2892-2L-e), platform xilinx_u280_xdma_201920_3, Vitis/Vivado 2021.1, XRT 2.13. Shared machine - the card is reprogrammed by other users between sessions.</t>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Mixed-sparsity matrix - runtime reconfiguration WITHIN a single run</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>One matrix split into four consecutive quarters, each at a different sparsity: 2:4, then 2:8, then 2:16, then 2:32, with an equal number of rows in each. Measured on the 300 MHz bitstream. NOTHING IN THE RTL CHANGED for this - the engine already re-derives its freeze length from the sparsity code at every activation-window boundary (top_module_2N.vhd, `case sparsity_next`), and the host already read the code per lap. Only the stimulus generator gained a --mix flag.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>THE SPLIT GRANULARITY IS THE LAP. One lap = 64 rows = one output beat, and sparsity must hold constant across a lap because a lap is one row's complete dot product - every window of the activation vector contributes to the same accumulation. The host rejects a mid-lap change outright.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr"/>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="42" t="inlineStr">
-        <is>
-          <t>SYSTEM UNDER TEST</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="44" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
-        <is>
-          <t>dense : 10 x krnl_mm2s -&gt; krnl_gemv_dense (ap_ctrl_none, free-running) -&gt; 4 x krnl_s2mm. 14 HBM pseudo-channels. 300 MHz, WNS +0.022 ns.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
-        <is>
-          <t>sparse: 13 x krnl_mm2s -&gt; krnl_gemv_sparse -&gt; 4 x krnl_s2mm. 17 HBM pseudo-channels (8 weight + 3 index + 2 activation in, 4 out). 300 MHz, WNS 0.000 ns - a genuine pass (zero failing endpoints) but with NO margin, which should be stated as such.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
-        <is>
-          <t>The data-mover kernels are the SAME BINARIES in both systems - not rebuilt - so the comparison isolates the compute engine.</t>
-        </is>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>1. THE SCHEDULE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Sparsity</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Freeze (cyc/window)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Beats/lap</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Laps</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Weight beats</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" s="25" t="n">
+        <v>256</v>
+      </c>
+      <c r="E7" s="25" t="n">
+        <v>4096</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>262144</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>1048576</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2:8</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="25" t="n">
+        <v>128</v>
+      </c>
+      <c r="E8" s="25" t="n">
+        <v>4096</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>262144</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>524288</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2:16</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="25" t="n">
+        <v>64</v>
+      </c>
+      <c r="E9" s="25" t="n">
+        <v>4096</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>262144</v>
+      </c>
+      <c r="G9" s="25" t="n">
+        <v>262144</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
+      <c r="A10" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2:32</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="25" t="n">
+        <v>32</v>
+      </c>
+      <c r="E10" s="25" t="n">
+        <v>4096</v>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>262144</v>
+      </c>
+      <c r="G10" s="25" t="n">
+        <v>131072</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="42" t="inlineStr">
         <is>
-          <t>WHY RAW PER-RUN NUMBERS ARE NOT QUOTED</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>A single run is dominated by XRT launch overhead: the first sparse hardware run measured a 460 us kernel span for TWO weight beats, ~99.99% scheduling. The fitted intercepts put the fixed overhead at 458-686 us regardless of design.</t>
-        </is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B11" s="43" t="inlineStr"/>
+      <c r="C11" s="43" t="inlineStr"/>
+      <c r="D11" s="43" t="inlineStr"/>
+      <c r="E11" s="44" t="n">
+        <v>16384</v>
+      </c>
+      <c r="F11" s="44" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="G11" s="44" t="n">
+        <v>1966080</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="42" t="inlineStr">
-        <is>
-          <t>METHOD</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>1. Four problem sizes spanning an IDENTICAL beat range in every configuration: 262,144 -&gt; 2,097,152 weight beats.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>2. Each size run 15-25 times (sparse) / 5 (dense); the BEST kernel span is kept. Best, not mean: the machine is shared, so slow samples are contention rather than the design.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="44" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
-        <is>
-          <t>3. Timing from OpenCL profiling events on the kernels (earliest CU start -&gt; latest CU end), never wall clock - loading an xclbin triggers FPGA reconfiguration, which is seconds and non-deterministic.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="44" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
-        <is>
-          <t>4. A least-squares fit t(beats) = overhead + beats x slope over all four sizes. The SLOPE is the marginal cost per beat and is what every headline figure derives from; the INTERCEPT is the fixed launch overhead.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="44" customHeight="1">
-      <c r="A19" s="24" t="inlineStr">
-        <is>
-          <t>5. Differential rows in the per-design sheets are the same quantity from adjacent size pairs only. They agree with the fit but are noisier - several report beats/cycle marginally ABOVE 1.0, which is physically impossible and is best-of estimator optimism on a single lucky sample, not a real measurement.</t>
-        </is>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2. IS THE RUN THE SUM OF ITS PARTS? - the scientific claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Each quarter SHOULD cost its own uniform per-beat rate. Predicting the whole run from the four independent uniform fits, with no fitting and no free parameters:</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Weight beats</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>us/beat (its own uniform fit)</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Predicted compute (us)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="B16" s="25" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="C16" s="37" t="n">
+        <v>0.003406</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>3571.4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>2:8</t>
+        </is>
+      </c>
+      <c r="B17" s="25" t="n">
+        <v>524288</v>
+      </c>
+      <c r="C17" s="37" t="n">
+        <v>0.003414</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>1789.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>2:16</t>
+        </is>
+      </c>
+      <c r="B18" s="25" t="n">
+        <v>262144</v>
+      </c>
+      <c r="C18" s="37" t="n">
+        <v>0.00344</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>901.8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>2:32</t>
+        </is>
+      </c>
+      <c r="B19" s="25" t="n">
+        <v>131072</v>
+      </c>
+      <c r="C19" s="37" t="n">
+        <v>0.003459</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>453.4</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="inlineStr"/>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="42" t="inlineStr">
-        <is>
-          <t>CORRECTNESS</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="44" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
-        <is>
-          <t>Throughput stimulus is synthetic and carries NO golden model - it exists only to generate beats. That is legitimate because the datapath's timing is data-independent: the gather is a mux (delay independent of which index it selects), the Xilinx FP operators are configured with Maximum_Latency, and there is no data-dependent control flow. Only beat COUNTS affect run length.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="44" customHeight="1">
-      <c r="A23" s="24" t="inlineStr">
-        <is>
-          <t>Correctness is established separately, on small cases, by the Python golden model - bit-exact on hardware at all four sparsities AND in a runtime-reconfiguration run where the sparsity changes three times mid-calculation with no reload. Re-verified on the 300 MHz bitstream before any number here was recorded. The same golden model validated behavioural simulation, post-implementation simulation, hardware emulation and silicon, unchanged throughout.</t>
-        </is>
+      <c r="A20" s="42" t="inlineStr">
+        <is>
+          <t>predicted total</t>
+        </is>
+      </c>
+      <c r="B20" s="43" t="inlineStr"/>
+      <c r="C20" s="43" t="inlineStr"/>
+      <c r="D20" s="45" t="n">
+        <v>6716.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Measured kernel span (mean of 3)</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="n">
+        <v>7417.217</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Measured kernel span (best of 3)</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="n">
+        <v>7400.701</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="24" t="inlineStr"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="42" t="inlineStr">
-        <is>
-          <t>A HYPOTHESIS THAT WAS WRONG - recorded so it is not repeated</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="44" customHeight="1">
-      <c r="A26" s="24" t="inlineStr">
-        <is>
-          <t>An earlier, noisier sweep (smaller sizes, 5 reps, 30-60% spreads) showed beats/cycle apparently FALLING with sparsity - 0.969 / 0.831 / 0.879 / 0.787 - and this was attributed to the output path saturating at 2:32, where the freeze is 1 cycle so a flush occurs every cycle. That was MEASUREMENT NOISE, not an effect. Re-measured properly it is flat and near roofline at both clocks. There is no output-path bottleneck. The tell was present and missed: three differential rows in that data reported beats/cycle above 1.0, which is impossible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="24" t="inlineStr"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="42" t="inlineStr">
-        <is>
-          <t>POWER MEASUREMENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="44" customHeight="1">
-      <c r="A29" s="24" t="inlineStr">
-        <is>
-          <t>One calculation lasts 7-8 ms while `xbutil examine` takes ~1 s, so a 1 Hz instrument cannot sample a single run - and a plain run is ~85% H2D transfer anyway. Both hosts therefore take a soak argument: re-enqueue every CU back-to-back for 60 s with buffers ALREADY RESIDENT (no transfers), printing the window as epoch seconds so the sampler clips to exactly the load. ~54 samples per run survive the 6 s warm-up trim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="44" customHeight="1">
-      <c r="A30" s="24" t="inlineStr">
-        <is>
-          <t>The warm-up trim is not cosmetic: on a 5 s trial a sample taken just after the load began read 28.94 W, BELOW the 29.30 W idle mean, because the card's satellite controller polls its sensors slowly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="44" customHeight="1">
-      <c r="A31" s="24" t="inlineStr">
-        <is>
-          <t>The idle baseline is taken AFTER the host exits, with the same bitstream still programmed - so leakage, clock trees and the platform are held constant and the difference isolates the work. The reading taken BEFORE the host runs is NOT a valid baseline: it reflects whatever design was previously loaded.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="44" customHeight="1">
-      <c r="A32" s="24" t="inlineStr">
-        <is>
-          <t>Board power = the two 12 V input rails; VCCINT = the FPGA core rail, a SUBSET of it downstream of the regulators. Verified: 12 V Aux + 12 V PCIe reconstruct the reported board total exactly. Never sum the three. Only 3 of the U280's 14 rails report current, so only those three yield power.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="44" customHeight="1">
-      <c r="A33" s="24" t="inlineStr">
-        <is>
-          <t>Host/CPU power is deliberately NOT measured. The host does identical work in both cases - same movers, same transfers, same OpenCL calls - so it cannot discriminate between the designs, and reporting it would add a number that looks like evidence.</t>
-        </is>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Implied launch overhead (mean)</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="n">
+        <v>700.7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Launch overhead seen in uniform runs</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>457.9 - 686.0 us</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>THE MIXED MATRIX COSTS THE SUM OF ITS SEGMENTS PLUS THE ORDINARY FIXED OVERHEAD. The best span implies 684.0 us of overhead, inside the range observed across every uniform run; the mean implies 700.5 us, 2% above it - exactly what a mean should do when the comparison values are best-of-N fit intercepts. No penalty is paid at the three reconfiguration boundaries. Had the engine stalled to re-arm, or fallen back to the densest segment's freeze length, the span would be hundreds to thousands of microseconds longer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>3. THE THREE REPETITIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Kernel span (us)</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Bandwidth (GB/s)</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Mrow/s</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>beats/cycle (raw)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>7400.701</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>93.79600000000001</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>141.686</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>0.886</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" s="11" t="n">
+        <v>7421.583</v>
+      </c>
+      <c r="C32" s="11" t="n">
+        <v>93.533</v>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>141.287</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>0.883</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" s="11" t="n">
+        <v>7429.368</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>93.435</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>141.139</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>0.882</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24" t="inlineStr"/>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="42" t="inlineStr">
-        <is>
-          <t>KNOWN CAVEATS</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="44" customHeight="1">
-      <c r="A36" s="24" t="inlineStr">
-        <is>
-          <t>* The 300 MHz sparse build closes with WNS exactly 0.000 ns - zero failing endpoints, but zero margin, against dense's +0.022. Correctness was re-verified on it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="44" customHeight="1">
-      <c r="A37" s="24" t="inlineStr">
-        <is>
-          <t>* R^2 is 0.9988-0.9994 at 300 MHz, marginally below the 0.999 threshold for 2:16. The cause is the smallest size in each sweep (25-32% spread from launch-overhead variance against 4-5% at the largest); more repetitions do not fix it. Independent replicate runs agreeing to 0.4-1.4% are the better uncertainty estimate - see Clock study.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="44" customHeight="1">
-      <c r="A38" s="24" t="inlineStr">
-        <is>
-          <t>* V = 1024 elements (32 activation windows) throughout. Vector length was not swept.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="44" customHeight="1">
-      <c r="A39" s="24" t="inlineStr">
-        <is>
-          <t>* The 225 MHz sparse figures come from a DIFFERENT bitstream (no floorplan). They are a valid second data point, not an alternative measurement of the same design.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="44" customHeight="1">
-      <c r="A40" s="24" t="inlineStr">
-        <is>
-          <t>* Power sampling at ~1 Hz measures STEADY STATE only; nothing transient is visible. Board power also includes fans, which are thermally controlled and drift.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="44" customHeight="1">
-      <c r="A41" s="24" t="inlineStr">
-        <is>
-          <t>* The dynamic power deltas (4-5 W) are differences of large numbers (~31-35 W) and are the least precise quantity reported. Standard errors are in the raw CSV and should be quoted with them. The energy-per-row figures, which divide a LOAD power by a measured throughput, are far better conditioned.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="44" customHeight="1">
-      <c r="A42" s="24" t="inlineStr">
-        <is>
-          <t>* Dense was measured twice; dense_300MHz.csv is the run used here. An earlier run recorded in INTEGRATION_STEPS.md S22 gives a 38.17 Mrow/s DIFFERENTIAL. Use the FIT (36.99), because every sparse figure is a fit and mixing estimators across the two sides of a comparison is indefensible. They agree on the physics (~1 beat/cycle).</t>
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="B34" s="46" t="n">
+        <v>0.00387</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>4. HEADLINE, AVERAGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Matrix</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>1,048,576 x 1,024</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Latency, HBM-&gt;HBM (us, avg of 3)</t>
+        </is>
+      </c>
+      <c r="B39" s="18" t="n">
+        <v>7417.217</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Effective GFLOPS</t>
+        </is>
+      </c>
+      <c r="B40" s="47" t="n">
+        <v>289.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>HBM bandwidth (GB/s)</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="n">
+        <v>93.58799999999999</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Throughput (Mrow/s)</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="n">
+        <v>141.371</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>beats/cycle, OVERHEAD-CORRECTED</t>
+        </is>
+      </c>
+      <c r="B43" s="35" t="n">
+        <v>0.9757</v>
+      </c>
+    </row>
+    <row r="45" ht="58" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>DO NOT QUOTE THE HOST'S PRINTED beats/cycle OF 0.886 NEXT TO THE OTHER TABLES. That is a single-shot figure that still contains launch overhead, whereas every beats/cycle elsewhere in this workbook is fit-derived with overhead removed. Corrected the same way - 6,553.6 us ideal against 6,716.7 us of compute - this run achieves 0.9757, indistinguishable from the uniform runs (0.964-0.986). It is the one number here that invites a wrong question.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="44" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>WHAT THIS PROVES, AND WHAT IT DOES NOT. It proves correct runtime reconfiguration and correct timing in every segment. It does NOT prove bit-exactness: this is timing stimulus with no golden model, so the output.txt it writes must NOT be fed to compare_gemv4_py36.py - that would fail for the wrong reason. Bit-exact mixed-sparsity verification needs gemv4_cosim_gen.py extended to emit a segmented golden.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A27:H27"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7924,458 +9440,1955 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:AF23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="21" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="28" max="28"/>
+    <col width="20" customWidth="1" min="29" max="29"/>
+    <col width="26" customWidth="1" min="30" max="30"/>
+    <col width="26" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>dense_gemv @ 300 MHz  -  source: dense_300MHz.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="43" t="inlineStr">
-        <is>
-          <t>Rows 'a-&gt;b' are differentials between adjacent sizes (launch overhead cancels). Row 'FIT' is the least-squares fit: Best us = FIXED OVERHEAD, Mean us = slope in us/beat, Worst us = R^2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Size / pair</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Weight beats</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Rows</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Best us</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Mean us</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Worst us</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Spread %</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Reps</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>Ideal us</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>Bytes in</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>of which index</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>Bytes out</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>Mrow/s</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>GB/s</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>beats/cycle</t>
-        </is>
-      </c>
+          <t>Every measured configuration, one row each - the charting table</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>WIDE format on purpose: one row per configuration, every metric a column, so a chart is a column selection. The `estimator` column is load-bearing - sweep_fit numbers are marginal (launch overhead removed), power_soak numbers are sustained (overhead included), and mixed_run_avg3 is the mean of three single runs. NEVER chart one estimator against another; they differ by 5-6% for identical hardware.  Source: GEMV_Master_Results.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>clock_mhz</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>sparsity</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>sparsity_order</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>sparsity_M</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>estimator</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>M_rows</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>N_cols</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>weight_beats</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>beats_per_row</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>latency_avg_us</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>latency_best_us</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>bandwidth_avg_GBs</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>bandwidth_roofline_GBs</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>pct_of_roofline</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>GFLOPS_effective</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>GFLOPS_actual</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>Mrow_s</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>beats_per_cycle</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>input_PCs</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>DSPs</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>GFLOPS_eff_per_DSP</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr">
+        <is>
+          <t>board_load_W</t>
+        </is>
+      </c>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>board_idle_W</t>
+        </is>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>board_dynamic_W</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="inlineStr">
+        <is>
+          <t>vccint_load_W</t>
+        </is>
+      </c>
+      <c r="AA3" s="4" t="inlineStr">
+        <is>
+          <t>vccint_idle_W</t>
+        </is>
+      </c>
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>vccint_dynamic_W</t>
+        </is>
+      </c>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>noncore_dynamic_W</t>
+        </is>
+      </c>
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t>energy_nJ_per_row_board</t>
+        </is>
+      </c>
+      <c r="AE3" s="4" t="inlineStr">
+        <is>
+          <t>energy_nJ_per_row_vccint</t>
+        </is>
+      </c>
+      <c r="AF3" s="4" t="inlineStr">
+        <is>
+          <t>GMAC_per_W</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
+      <c r="B4" s="48" t="n">
+        <v>300</v>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
+      <c r="D4" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="10" t="inlineStr"/>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>sweep_fit</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="n">
+        <v>262144</v>
+      </c>
+      <c r="H4" s="25" t="n">
+        <v>1024</v>
+      </c>
+      <c r="I4" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="J4" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" s="48" t="n">
+        <v>7621.5</v>
+      </c>
+      <c r="L4" s="48" t="n">
+        <v>7559.1</v>
+      </c>
+      <c r="M4" s="48" t="n">
+        <v>70.44</v>
+      </c>
+      <c r="N4" s="48" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="O4" s="48" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="P4" s="48" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="Q4" s="48" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="R4" s="48" t="n">
+        <v>36.988</v>
+      </c>
+      <c r="S4" s="48" t="n">
+        <v>0.9863</v>
+      </c>
+      <c r="T4" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="U4" s="48" t="n">
+        <v>512</v>
+      </c>
+      <c r="V4" s="48" t="n">
+        <v>0.1376</v>
+      </c>
+      <c r="W4" s="10" t="inlineStr"/>
+      <c r="X4" s="10" t="inlineStr"/>
+      <c r="Y4" s="10" t="inlineStr"/>
+      <c r="Z4" s="10" t="inlineStr"/>
+      <c r="AA4" s="10" t="inlineStr"/>
+      <c r="AB4" s="10" t="inlineStr"/>
+      <c r="AC4" s="10" t="inlineStr"/>
+      <c r="AD4" s="10" t="inlineStr"/>
+      <c r="AE4" s="10" t="inlineStr"/>
+      <c r="AF4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="B5" s="25" t="n">
-        <v>262144</v>
-      </c>
-      <c r="C5" s="25" t="n">
-        <v>32768</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>1350.042</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>1378.399</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>1420.373</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H5" s="6" t="n">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="B5" s="48" t="n">
+        <v>300</v>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="D5" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>sweep_fit</t>
+        </is>
+      </c>
+      <c r="G5" s="25" t="n">
+        <v>524288</v>
+      </c>
+      <c r="H5" s="25" t="n">
+        <v>1024</v>
+      </c>
+      <c r="I5" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="J5" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" s="48" t="n">
+        <v>7839.7</v>
+      </c>
+      <c r="L5" s="48" t="n">
+        <v>7774.5</v>
+      </c>
+      <c r="M5" s="48" t="n">
+        <v>94.16</v>
+      </c>
+      <c r="N5" s="48" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="O5" s="48" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="P5" s="48" t="n">
+        <v>137</v>
+      </c>
+      <c r="Q5" s="48" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="R5" s="48" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="S5" s="48" t="n">
+        <v>0.9787</v>
+      </c>
+      <c r="T5" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="U5" s="48" t="n">
+        <v>512</v>
+      </c>
+      <c r="V5" s="48" t="n">
+        <v>0.2675</v>
+      </c>
+      <c r="W5" s="10" t="inlineStr"/>
+      <c r="X5" s="10" t="inlineStr"/>
+      <c r="Y5" s="10" t="inlineStr"/>
+      <c r="Z5" s="10" t="inlineStr"/>
+      <c r="AA5" s="10" t="inlineStr"/>
+      <c r="AB5" s="10" t="inlineStr"/>
+      <c r="AC5" s="10" t="inlineStr"/>
+      <c r="AD5" s="10" t="inlineStr"/>
+      <c r="AE5" s="10" t="inlineStr"/>
+      <c r="AF5" s="10" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="B6" s="48" t="n">
+        <v>300</v>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>2:8</t>
+        </is>
+      </c>
+      <c r="D6" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>sweep_fit</t>
+        </is>
+      </c>
+      <c r="G6" s="25" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="H6" s="25" t="n">
+        <v>1024</v>
+      </c>
+      <c r="I6" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="J6" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="48" t="n">
+        <v>7871.6</v>
+      </c>
+      <c r="L6" s="48" t="n">
+        <v>7693.2</v>
+      </c>
+      <c r="M6" s="48" t="n">
+        <v>93.78</v>
+      </c>
+      <c r="N6" s="48" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="O6" s="48" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="P6" s="48" t="n">
+        <v>272.8</v>
+      </c>
+      <c r="Q6" s="48" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="R6" s="48" t="n">
+        <v>146.437</v>
+      </c>
+      <c r="S6" s="48" t="n">
+        <v>0.9762</v>
+      </c>
+      <c r="T6" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="U6" s="48" t="n">
+        <v>512</v>
+      </c>
+      <c r="V6" s="48" t="n">
+        <v>0.5328000000000001</v>
+      </c>
+      <c r="W6" s="10" t="inlineStr"/>
+      <c r="X6" s="10" t="inlineStr"/>
+      <c r="Y6" s="10" t="inlineStr"/>
+      <c r="Z6" s="10" t="inlineStr"/>
+      <c r="AA6" s="10" t="inlineStr"/>
+      <c r="AB6" s="10" t="inlineStr"/>
+      <c r="AC6" s="10" t="inlineStr"/>
+      <c r="AD6" s="10" t="inlineStr"/>
+      <c r="AE6" s="10" t="inlineStr"/>
+      <c r="AF6" s="10" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="B7" s="48" t="n">
+        <v>300</v>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>2:16</t>
+        </is>
+      </c>
+      <c r="D7" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="48" t="n">
+        <v>16</v>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>sweep_fit</t>
+        </is>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="H7" s="25" t="n">
+        <v>1024</v>
+      </c>
+      <c r="I7" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="J7" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="25" t="n">
+        <v>7923</v>
+      </c>
+      <c r="L7" s="48" t="n">
+        <v>7777.4</v>
+      </c>
+      <c r="M7" s="48" t="n">
+        <v>93.17</v>
+      </c>
+      <c r="N7" s="48" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="O7" s="48" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="P7" s="48" t="n">
+        <v>542.1</v>
+      </c>
+      <c r="Q7" s="48" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="R7" s="48" t="n">
+        <v>290.729</v>
+      </c>
+      <c r="S7" s="48" t="n">
+        <v>0.9691</v>
+      </c>
+      <c r="T7" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="U7" s="48" t="n">
+        <v>512</v>
+      </c>
+      <c r="V7" s="48" t="n">
+        <v>1.0588</v>
+      </c>
+      <c r="W7" s="10" t="inlineStr"/>
+      <c r="X7" s="10" t="inlineStr"/>
+      <c r="Y7" s="10" t="inlineStr"/>
+      <c r="Z7" s="10" t="inlineStr"/>
+      <c r="AA7" s="10" t="inlineStr"/>
+      <c r="AB7" s="10" t="inlineStr"/>
+      <c r="AC7" s="10" t="inlineStr"/>
+      <c r="AD7" s="10" t="inlineStr"/>
+      <c r="AE7" s="10" t="inlineStr"/>
+      <c r="AF7" s="10" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="B8" s="48" t="n">
+        <v>300</v>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>2:32</t>
+        </is>
+      </c>
+      <c r="D8" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="I5" s="11" t="n">
-        <v>873.813</v>
-      </c>
-      <c r="J5" s="25" t="n">
-        <v>67110912</v>
-      </c>
-      <c r="K5" s="25" t="inlineStr"/>
-      <c r="L5" s="25" t="n">
-        <v>65536</v>
-      </c>
-      <c r="M5" s="11" t="n">
-        <v>24.2718</v>
-      </c>
-      <c r="N5" s="11" t="n">
-        <v>49.7588</v>
-      </c>
-      <c r="O5" s="11" t="n">
-        <v>0.6472</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>1024</t>
-        </is>
-      </c>
-      <c r="B6" s="25" t="n">
+      <c r="E8" s="48" t="n">
+        <v>32</v>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>sweep_fit</t>
+        </is>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>4194304</v>
+      </c>
+      <c r="H8" s="25" t="n">
+        <v>1024</v>
+      </c>
+      <c r="I8" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="J8" s="48" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K8" s="48" t="n">
+        <v>8047.5</v>
+      </c>
+      <c r="L8" s="48" t="n">
+        <v>7905.6</v>
+      </c>
+      <c r="M8" s="48" t="n">
+        <v>91.73</v>
+      </c>
+      <c r="N8" s="48" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="O8" s="48" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="P8" s="48" t="n">
+        <v>1067.4</v>
+      </c>
+      <c r="Q8" s="48" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="R8" s="48" t="n">
+        <v>578.162</v>
+      </c>
+      <c r="S8" s="48" t="n">
+        <v>0.9636</v>
+      </c>
+      <c r="T8" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="U8" s="48" t="n">
+        <v>512</v>
+      </c>
+      <c r="V8" s="48" t="n">
+        <v>2.0848</v>
+      </c>
+      <c r="W8" s="10" t="inlineStr"/>
+      <c r="X8" s="10" t="inlineStr"/>
+      <c r="Y8" s="10" t="inlineStr"/>
+      <c r="Z8" s="10" t="inlineStr"/>
+      <c r="AA8" s="10" t="inlineStr"/>
+      <c r="AB8" s="10" t="inlineStr"/>
+      <c r="AC8" s="10" t="inlineStr"/>
+      <c r="AD8" s="10" t="inlineStr"/>
+      <c r="AE8" s="10" t="inlineStr"/>
+      <c r="AF8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="B9" s="48" t="n">
+        <v>225</v>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="D9" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>sweep_fit</t>
+        </is>
+      </c>
+      <c r="G9" s="25" t="n">
         <v>524288</v>
       </c>
-      <c r="C6" s="25" t="n">
-        <v>65536</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>2248.313</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>2343.055</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>2509.826</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="H6" s="6" t="n">
+      <c r="H9" s="25" t="n">
+        <v>1024</v>
+      </c>
+      <c r="I9" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="J9" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" s="48" t="n">
+        <v>10139.8</v>
+      </c>
+      <c r="L9" s="48" t="n">
+        <v>9977.4</v>
+      </c>
+      <c r="M9" s="48" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="N9" s="48" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="O9" s="48" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="P9" s="48" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="Q9" s="48" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="R9" s="48" t="n">
+        <v>56.033</v>
+      </c>
+      <c r="S9" s="48" t="n">
+        <v>0.9961</v>
+      </c>
+      <c r="T9" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="U9" s="48" t="n">
+        <v>512</v>
+      </c>
+      <c r="V9" s="48" t="n">
+        <v>0.2068</v>
+      </c>
+      <c r="W9" s="10" t="inlineStr"/>
+      <c r="X9" s="10" t="inlineStr"/>
+      <c r="Y9" s="10" t="inlineStr"/>
+      <c r="Z9" s="10" t="inlineStr"/>
+      <c r="AA9" s="10" t="inlineStr"/>
+      <c r="AB9" s="10" t="inlineStr"/>
+      <c r="AC9" s="10" t="inlineStr"/>
+      <c r="AD9" s="10" t="inlineStr"/>
+      <c r="AE9" s="10" t="inlineStr"/>
+      <c r="AF9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="B10" s="48" t="n">
+        <v>225</v>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>2:8</t>
+        </is>
+      </c>
+      <c r="D10" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>sweep_fit</t>
+        </is>
+      </c>
+      <c r="G10" s="25" t="n">
+        <v>1048576</v>
+      </c>
+      <c r="H10" s="25" t="n">
+        <v>1024</v>
+      </c>
+      <c r="I10" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="J10" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="48" t="n">
+        <v>10281.8</v>
+      </c>
+      <c r="L10" s="48" t="n">
+        <v>10101.2</v>
+      </c>
+      <c r="M10" s="48" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="N10" s="48" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="O10" s="48" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="P10" s="48" t="n">
+        <v>208.9</v>
+      </c>
+      <c r="Q10" s="48" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="R10" s="48" t="n">
+        <v>109.874</v>
+      </c>
+      <c r="S10" s="48" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="T10" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="U10" s="48" t="n">
+        <v>512</v>
+      </c>
+      <c r="V10" s="48" t="n">
+        <v>0.4079</v>
+      </c>
+      <c r="W10" s="10" t="inlineStr"/>
+      <c r="X10" s="10" t="inlineStr"/>
+      <c r="Y10" s="10" t="inlineStr"/>
+      <c r="Z10" s="10" t="inlineStr"/>
+      <c r="AA10" s="10" t="inlineStr"/>
+      <c r="AB10" s="10" t="inlineStr"/>
+      <c r="AC10" s="10" t="inlineStr"/>
+      <c r="AD10" s="10" t="inlineStr"/>
+      <c r="AE10" s="10" t="inlineStr"/>
+      <c r="AF10" s="10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="B11" s="48" t="n">
+        <v>225</v>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>2:16</t>
+        </is>
+      </c>
+      <c r="D11" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="48" t="n">
+        <v>16</v>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>sweep_fit</t>
+        </is>
+      </c>
+      <c r="G11" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="H11" s="25" t="n">
+        <v>1024</v>
+      </c>
+      <c r="I11" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="J11" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="48" t="n">
+        <v>10287.7</v>
+      </c>
+      <c r="L11" s="48" t="n">
+        <v>10099.3</v>
+      </c>
+      <c r="M11" s="48" t="n">
+        <v>71.76000000000001</v>
+      </c>
+      <c r="N11" s="48" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="O11" s="48" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="P11" s="48" t="n">
+        <v>417.5</v>
+      </c>
+      <c r="Q11" s="48" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="R11" s="48" t="n">
+        <v>220.347</v>
+      </c>
+      <c r="S11" s="48" t="n">
+        <v>0.9792999999999999</v>
+      </c>
+      <c r="T11" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="U11" s="48" t="n">
+        <v>512</v>
+      </c>
+      <c r="V11" s="48" t="n">
+        <v>0.8154</v>
+      </c>
+      <c r="W11" s="10" t="inlineStr"/>
+      <c r="X11" s="10" t="inlineStr"/>
+      <c r="Y11" s="10" t="inlineStr"/>
+      <c r="Z11" s="10" t="inlineStr"/>
+      <c r="AA11" s="10" t="inlineStr"/>
+      <c r="AB11" s="10" t="inlineStr"/>
+      <c r="AC11" s="10" t="inlineStr"/>
+      <c r="AD11" s="10" t="inlineStr"/>
+      <c r="AE11" s="10" t="inlineStr"/>
+      <c r="AF11" s="10" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="B12" s="48" t="n">
+        <v>225</v>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>2:32</t>
+        </is>
+      </c>
+      <c r="D12" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="I6" s="11" t="n">
-        <v>1747.627</v>
-      </c>
-      <c r="J6" s="25" t="n">
-        <v>134219776</v>
-      </c>
-      <c r="K6" s="25" t="inlineStr"/>
-      <c r="L6" s="25" t="n">
-        <v>131072</v>
-      </c>
-      <c r="M6" s="11" t="n">
-        <v>29.149</v>
-      </c>
-      <c r="N6" s="11" t="n">
-        <v>59.7563</v>
-      </c>
-      <c r="O6" s="11" t="n">
-        <v>0.7773</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="B7" s="25" t="n">
+      <c r="E12" s="48" t="n">
+        <v>32</v>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>sweep_fit</t>
+        </is>
+      </c>
+      <c r="G12" s="25" t="n">
+        <v>4194304</v>
+      </c>
+      <c r="H12" s="25" t="n">
+        <v>1024</v>
+      </c>
+      <c r="I12" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="J12" s="48" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K12" s="48" t="n">
+        <v>10403.4</v>
+      </c>
+      <c r="L12" s="48" t="n">
+        <v>10231.3</v>
+      </c>
+      <c r="M12" s="48" t="n">
+        <v>70.95999999999999</v>
+      </c>
+      <c r="N12" s="48" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="O12" s="48" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="P12" s="48" t="n">
+        <v>825.7</v>
+      </c>
+      <c r="Q12" s="48" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="R12" s="48" t="n">
+        <v>431.132</v>
+      </c>
+      <c r="S12" s="48" t="n">
+        <v>0.9581</v>
+      </c>
+      <c r="T12" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="U12" s="48" t="n">
+        <v>512</v>
+      </c>
+      <c r="V12" s="48" t="n">
+        <v>1.6127</v>
+      </c>
+      <c r="W12" s="10" t="inlineStr"/>
+      <c r="X12" s="10" t="inlineStr"/>
+      <c r="Y12" s="10" t="inlineStr"/>
+      <c r="Z12" s="10" t="inlineStr"/>
+      <c r="AA12" s="10" t="inlineStr"/>
+      <c r="AB12" s="10" t="inlineStr"/>
+      <c r="AC12" s="10" t="inlineStr"/>
+      <c r="AD12" s="10" t="inlineStr"/>
+      <c r="AE12" s="10" t="inlineStr"/>
+      <c r="AF12" s="10" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
+      <c r="B13" s="48" t="n">
+        <v>300</v>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
+      <c r="D13" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="10" t="inlineStr"/>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>power_soak</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr"/>
+      <c r="H13" s="25" t="n">
+        <v>1024</v>
+      </c>
+      <c r="I13" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="J13" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="K13" s="10" t="inlineStr"/>
+      <c r="L13" s="10" t="inlineStr"/>
+      <c r="M13" s="10" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
+      <c r="O13" s="10" t="inlineStr"/>
+      <c r="P13" s="48" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="Q13" s="48" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="R13" s="48" t="n">
+        <v>35.265</v>
+      </c>
+      <c r="S13" s="10" t="inlineStr"/>
+      <c r="T13" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="U13" s="48" t="n">
+        <v>512</v>
+      </c>
+      <c r="V13" s="48" t="n">
+        <v>0.1411</v>
+      </c>
+      <c r="W13" s="48" t="n">
+        <v>31.297</v>
+      </c>
+      <c r="X13" s="48" t="n">
+        <v>26.924</v>
+      </c>
+      <c r="Y13" s="48" t="n">
+        <v>4.373</v>
+      </c>
+      <c r="Z13" s="48" t="n">
+        <v>7.731</v>
+      </c>
+      <c r="AA13" s="48" t="n">
+        <v>6.657</v>
+      </c>
+      <c r="AB13" s="48" t="n">
+        <v>1.074</v>
+      </c>
+      <c r="AC13" s="48" t="n">
+        <v>3.139</v>
+      </c>
+      <c r="AD13" s="48" t="n">
+        <v>887.5</v>
+      </c>
+      <c r="AE13" s="48" t="n">
+        <v>219.2</v>
+      </c>
+      <c r="AF13" s="48" t="n">
+        <v>1.154</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
+      <c r="B14" s="48" t="n">
+        <v>325</v>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
+      <c r="D14" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="10" t="inlineStr"/>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>power_soak</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr"/>
+      <c r="H14" s="25" t="n">
+        <v>1024</v>
+      </c>
+      <c r="I14" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="J14" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="K14" s="10" t="inlineStr"/>
+      <c r="L14" s="10" t="inlineStr"/>
+      <c r="M14" s="10" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
+      <c r="O14" s="10" t="inlineStr"/>
+      <c r="P14" s="48" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q14" s="48" t="n">
+        <v>78</v>
+      </c>
+      <c r="R14" s="48" t="n">
+        <v>38.094</v>
+      </c>
+      <c r="S14" s="10" t="inlineStr"/>
+      <c r="T14" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="U14" s="48" t="n">
+        <v>512</v>
+      </c>
+      <c r="V14" s="48" t="n">
+        <v>0.1524</v>
+      </c>
+      <c r="W14" s="48" t="n">
+        <v>31.724</v>
+      </c>
+      <c r="X14" s="48" t="n">
+        <v>27.077</v>
+      </c>
+      <c r="Y14" s="48" t="n">
+        <v>4.647</v>
+      </c>
+      <c r="Z14" s="48" t="n">
+        <v>7.809</v>
+      </c>
+      <c r="AA14" s="48" t="n">
+        <v>6.764</v>
+      </c>
+      <c r="AB14" s="48" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="AC14" s="48" t="n">
+        <v>3.446</v>
+      </c>
+      <c r="AD14" s="48" t="n">
+        <v>832.8</v>
+      </c>
+      <c r="AE14" s="48" t="n">
+        <v>205</v>
+      </c>
+      <c r="AF14" s="48" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="B15" s="48" t="n">
+        <v>300</v>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="D15" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>power_soak</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr"/>
+      <c r="H15" s="25" t="n">
+        <v>1024</v>
+      </c>
+      <c r="I15" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="J15" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" s="10" t="inlineStr"/>
+      <c r="L15" s="10" t="inlineStr"/>
+      <c r="M15" s="10" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
+      <c r="O15" s="10" t="inlineStr"/>
+      <c r="P15" s="48" t="n">
+        <v>142.9</v>
+      </c>
+      <c r="Q15" s="48" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="R15" s="48" t="n">
+        <v>69.771</v>
+      </c>
+      <c r="S15" s="10" t="inlineStr"/>
+      <c r="T15" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="U15" s="48" t="n">
+        <v>512</v>
+      </c>
+      <c r="V15" s="48" t="n">
+        <v>0.2791</v>
+      </c>
+      <c r="W15" s="48" t="n">
+        <v>35.442</v>
+      </c>
+      <c r="X15" s="48" t="n">
+        <v>30.138</v>
+      </c>
+      <c r="Y15" s="48" t="n">
+        <v>5.304</v>
+      </c>
+      <c r="Z15" s="48" t="n">
+        <v>7.756</v>
+      </c>
+      <c r="AA15" s="48" t="n">
+        <v>7.095</v>
+      </c>
+      <c r="AB15" s="48" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="AC15" s="48" t="n">
+        <v>4.544</v>
+      </c>
+      <c r="AD15" s="48" t="n">
+        <v>508</v>
+      </c>
+      <c r="AE15" s="48" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="AF15" s="48" t="n">
+        <v>2.016</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="B16" s="48" t="n">
+        <v>325</v>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="D16" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>power_soak</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr"/>
+      <c r="H16" s="25" t="n">
+        <v>1024</v>
+      </c>
+      <c r="I16" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="J16" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" s="10" t="inlineStr"/>
+      <c r="L16" s="10" t="inlineStr"/>
+      <c r="M16" s="10" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
+      <c r="O16" s="10" t="inlineStr"/>
+      <c r="P16" s="48" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="Q16" s="48" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="R16" s="48" t="n">
+        <v>75.919</v>
+      </c>
+      <c r="S16" s="10" t="inlineStr"/>
+      <c r="T16" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="U16" s="48" t="n">
+        <v>512</v>
+      </c>
+      <c r="V16" s="48" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="W16" s="48" t="n">
+        <v>35.994</v>
+      </c>
+      <c r="X16" s="48" t="n">
+        <v>30.165</v>
+      </c>
+      <c r="Y16" s="48" t="n">
+        <v>5.829</v>
+      </c>
+      <c r="Z16" s="48" t="n">
+        <v>7.911</v>
+      </c>
+      <c r="AA16" s="48" t="n">
+        <v>7.126</v>
+      </c>
+      <c r="AB16" s="48" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="AC16" s="48" t="n">
+        <v>4.927</v>
+      </c>
+      <c r="AD16" s="48" t="n">
+        <v>474.1</v>
+      </c>
+      <c r="AE16" s="48" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="AF16" s="48" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="B17" s="48" t="n">
+        <v>300</v>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>2:8</t>
+        </is>
+      </c>
+      <c r="D17" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>power_soak</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr"/>
+      <c r="H17" s="25" t="n">
+        <v>1024</v>
+      </c>
+      <c r="I17" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="J17" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" s="10" t="inlineStr"/>
+      <c r="L17" s="10" t="inlineStr"/>
+      <c r="M17" s="10" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
+      <c r="O17" s="10" t="inlineStr"/>
+      <c r="P17" s="48" t="n">
+        <v>285.2</v>
+      </c>
+      <c r="Q17" s="48" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="R17" s="48" t="n">
+        <v>139.266</v>
+      </c>
+      <c r="S17" s="10" t="inlineStr"/>
+      <c r="T17" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="U17" s="48" t="n">
+        <v>512</v>
+      </c>
+      <c r="V17" s="48" t="n">
+        <v>0.5571</v>
+      </c>
+      <c r="W17" s="48" t="n">
+        <v>35.327</v>
+      </c>
+      <c r="X17" s="48" t="n">
+        <v>30.115</v>
+      </c>
+      <c r="Y17" s="48" t="n">
+        <v>5.212</v>
+      </c>
+      <c r="Z17" s="48" t="n">
+        <v>7.823</v>
+      </c>
+      <c r="AA17" s="48" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="AB17" s="48" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="AC17" s="48" t="n">
+        <v>4.461</v>
+      </c>
+      <c r="AD17" s="48" t="n">
+        <v>253.7</v>
+      </c>
+      <c r="AE17" s="48" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="AF17" s="48" t="n">
+        <v>4.037</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="B18" s="48" t="n">
+        <v>325</v>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>2:8</t>
+        </is>
+      </c>
+      <c r="D18" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>power_soak</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr"/>
+      <c r="H18" s="25" t="n">
+        <v>1024</v>
+      </c>
+      <c r="I18" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="J18" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" s="10" t="inlineStr"/>
+      <c r="L18" s="10" t="inlineStr"/>
+      <c r="M18" s="10" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
+      <c r="O18" s="10" t="inlineStr"/>
+      <c r="P18" s="48" t="n">
+        <v>307.7</v>
+      </c>
+      <c r="Q18" s="48" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="R18" s="48" t="n">
+        <v>150.235</v>
+      </c>
+      <c r="S18" s="10" t="inlineStr"/>
+      <c r="T18" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="U18" s="48" t="n">
+        <v>512</v>
+      </c>
+      <c r="V18" s="48" t="n">
+        <v>0.6009</v>
+      </c>
+      <c r="W18" s="48" t="n">
+        <v>35.452</v>
+      </c>
+      <c r="X18" s="48" t="n">
+        <v>30.164</v>
+      </c>
+      <c r="Y18" s="48" t="n">
+        <v>5.288</v>
+      </c>
+      <c r="Z18" s="48" t="n">
+        <v>7.951</v>
+      </c>
+      <c r="AA18" s="48" t="n">
+        <v>7.177</v>
+      </c>
+      <c r="AB18" s="48" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="AC18" s="48" t="n">
+        <v>4.398</v>
+      </c>
+      <c r="AD18" s="48" t="n">
+        <v>236</v>
+      </c>
+      <c r="AE18" s="48" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="AF18" s="48" t="n">
+        <v>4.339</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="B19" s="48" t="n">
+        <v>300</v>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>2:16</t>
+        </is>
+      </c>
+      <c r="D19" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" s="48" t="n">
+        <v>16</v>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>power_soak</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr"/>
+      <c r="H19" s="25" t="n">
+        <v>1024</v>
+      </c>
+      <c r="I19" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="J19" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="10" t="inlineStr"/>
+      <c r="L19" s="10" t="inlineStr"/>
+      <c r="M19" s="10" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
+      <c r="O19" s="10" t="inlineStr"/>
+      <c r="P19" s="48" t="n">
+        <v>565</v>
+      </c>
+      <c r="Q19" s="48" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="R19" s="48" t="n">
+        <v>275.864</v>
+      </c>
+      <c r="S19" s="10" t="inlineStr"/>
+      <c r="T19" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="U19" s="48" t="n">
+        <v>512</v>
+      </c>
+      <c r="V19" s="48" t="n">
+        <v>1.1035</v>
+      </c>
+      <c r="W19" s="48" t="n">
+        <v>35.413</v>
+      </c>
+      <c r="X19" s="48" t="n">
+        <v>30.226</v>
+      </c>
+      <c r="Y19" s="48" t="n">
+        <v>5.187</v>
+      </c>
+      <c r="Z19" s="48" t="n">
+        <v>7.909</v>
+      </c>
+      <c r="AA19" s="48" t="n">
+        <v>7.172</v>
+      </c>
+      <c r="AB19" s="48" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="AC19" s="48" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="AD19" s="48" t="n">
+        <v>128.4</v>
+      </c>
+      <c r="AE19" s="48" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="AF19" s="48" t="n">
+        <v>7.977</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="B20" s="48" t="n">
+        <v>325</v>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>2:16</t>
+        </is>
+      </c>
+      <c r="D20" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="48" t="n">
+        <v>16</v>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>power_soak</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr"/>
+      <c r="H20" s="25" t="n">
+        <v>1024</v>
+      </c>
+      <c r="I20" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="J20" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="10" t="inlineStr"/>
+      <c r="L20" s="10" t="inlineStr"/>
+      <c r="M20" s="10" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
+      <c r="O20" s="10" t="inlineStr"/>
+      <c r="P20" s="48" t="n">
+        <v>609.2</v>
+      </c>
+      <c r="Q20" s="48" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="R20" s="48" t="n">
+        <v>297.452</v>
+      </c>
+      <c r="S20" s="10" t="inlineStr"/>
+      <c r="T20" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="U20" s="48" t="n">
+        <v>512</v>
+      </c>
+      <c r="V20" s="48" t="n">
+        <v>1.1898</v>
+      </c>
+      <c r="W20" s="48" t="n">
+        <v>36.084</v>
+      </c>
+      <c r="X20" s="48" t="n">
+        <v>30.201</v>
+      </c>
+      <c r="Y20" s="48" t="n">
+        <v>5.883</v>
+      </c>
+      <c r="Z20" s="48" t="n">
+        <v>8.037000000000001</v>
+      </c>
+      <c r="AA20" s="48" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="AB20" s="48" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="AC20" s="48" t="n">
+        <v>4.932</v>
+      </c>
+      <c r="AD20" s="48" t="n">
+        <v>121.3</v>
+      </c>
+      <c r="AE20" s="48" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF20" s="48" t="n">
+        <v>8.441000000000001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="B21" s="48" t="n">
+        <v>300</v>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>2:32</t>
+        </is>
+      </c>
+      <c r="D21" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" s="48" t="n">
+        <v>32</v>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>power_soak</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr"/>
+      <c r="H21" s="25" t="n">
+        <v>1024</v>
+      </c>
+      <c r="I21" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="J21" s="48" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K21" s="10" t="inlineStr"/>
+      <c r="L21" s="10" t="inlineStr"/>
+      <c r="M21" s="10" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
+      <c r="O21" s="10" t="inlineStr"/>
+      <c r="P21" s="25" t="n">
+        <v>1117</v>
+      </c>
+      <c r="Q21" s="48" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="R21" s="48" t="n">
+        <v>545.417</v>
+      </c>
+      <c r="S21" s="10" t="inlineStr"/>
+      <c r="T21" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="U21" s="48" t="n">
+        <v>512</v>
+      </c>
+      <c r="V21" s="48" t="n">
+        <v>2.1817</v>
+      </c>
+      <c r="W21" s="48" t="n">
+        <v>35.521</v>
+      </c>
+      <c r="X21" s="48" t="n">
+        <v>30.138</v>
+      </c>
+      <c r="Y21" s="48" t="n">
+        <v>5.383</v>
+      </c>
+      <c r="Z21" s="48" t="n">
+        <v>7.906</v>
+      </c>
+      <c r="AA21" s="48" t="n">
+        <v>7.249</v>
+      </c>
+      <c r="AB21" s="48" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="AC21" s="48" t="n">
+        <v>4.628</v>
+      </c>
+      <c r="AD21" s="48" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="AE21" s="48" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AF21" s="48" t="n">
+        <v>15.723</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="B22" s="48" t="n">
+        <v>325</v>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>2:32</t>
+        </is>
+      </c>
+      <c r="D22" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" s="48" t="n">
+        <v>32</v>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>power_soak</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr"/>
+      <c r="H22" s="25" t="n">
+        <v>1024</v>
+      </c>
+      <c r="I22" s="25" t="n">
+        <v>2097152</v>
+      </c>
+      <c r="J22" s="48" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K22" s="10" t="inlineStr"/>
+      <c r="L22" s="10" t="inlineStr"/>
+      <c r="M22" s="10" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
+      <c r="O22" s="10" t="inlineStr"/>
+      <c r="P22" s="48" t="n">
+        <v>1211.1</v>
+      </c>
+      <c r="Q22" s="48" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="R22" s="48" t="n">
+        <v>591.371</v>
+      </c>
+      <c r="S22" s="10" t="inlineStr"/>
+      <c r="T22" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="U22" s="48" t="n">
+        <v>512</v>
+      </c>
+      <c r="V22" s="48" t="n">
+        <v>2.3655</v>
+      </c>
+      <c r="W22" s="48" t="n">
+        <v>36.338</v>
+      </c>
+      <c r="X22" s="48" t="n">
+        <v>30.336</v>
+      </c>
+      <c r="Y22" s="48" t="n">
+        <v>6.002</v>
+      </c>
+      <c r="Z22" s="48" t="n">
+        <v>8.058</v>
+      </c>
+      <c r="AA22" s="48" t="n">
+        <v>7.261</v>
+      </c>
+      <c r="AB22" s="48" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="AC22" s="48" t="n">
+        <v>5.086</v>
+      </c>
+      <c r="AD22" s="48" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="AE22" s="48" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="AF22" s="48" t="n">
+        <v>16.665</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="B23" s="48" t="n">
+        <v>300</v>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>MIXED 2:4|2:8|2:16|2:32</t>
+        </is>
+      </c>
+      <c r="D23" s="48" t="n">
+        <v>99</v>
+      </c>
+      <c r="E23" s="10" t="inlineStr"/>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>mixed_run_avg3</t>
+        </is>
+      </c>
+      <c r="G23" s="25" t="n">
         <v>1048576</v>
       </c>
-      <c r="C7" s="25" t="n">
-        <v>131072</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>3962.545</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>4106.829</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>4211.676</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>3495.253</v>
-      </c>
-      <c r="J7" s="25" t="n">
-        <v>268437504</v>
-      </c>
-      <c r="K7" s="25" t="inlineStr"/>
-      <c r="L7" s="25" t="n">
-        <v>262144</v>
-      </c>
-      <c r="M7" s="11" t="n">
-        <v>33.0777</v>
-      </c>
-      <c r="N7" s="11" t="n">
-        <v>67.8099</v>
-      </c>
-      <c r="O7" s="11" t="n">
-        <v>0.8821</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>4096</t>
-        </is>
-      </c>
-      <c r="B8" s="25" t="n">
-        <v>2097152</v>
-      </c>
-      <c r="C8" s="25" t="n">
-        <v>262144</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>7559.144</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>7621.513</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>7669.501</v>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" s="11" t="n">
-        <v>6990.507</v>
-      </c>
-      <c r="J8" s="25" t="n">
-        <v>536872960</v>
-      </c>
-      <c r="K8" s="25" t="inlineStr"/>
-      <c r="L8" s="25" t="n">
-        <v>524288</v>
-      </c>
-      <c r="M8" s="11" t="n">
-        <v>34.6791</v>
-      </c>
-      <c r="N8" s="11" t="n">
-        <v>71.09229999999999</v>
-      </c>
-      <c r="O8" s="11" t="n">
-        <v>0.9248</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="44" t="inlineStr">
-        <is>
-          <t>512-&gt;1024</t>
-        </is>
-      </c>
-      <c r="B9" s="45" t="n">
-        <v>262144</v>
-      </c>
-      <c r="C9" s="45" t="n">
-        <v>32768</v>
-      </c>
-      <c r="D9" s="46" t="n">
-        <v>898.271</v>
-      </c>
-      <c r="E9" s="46" t="inlineStr"/>
-      <c r="F9" s="46" t="inlineStr"/>
-      <c r="G9" s="46" t="inlineStr"/>
-      <c r="H9" s="47" t="inlineStr"/>
-      <c r="I9" s="46" t="n">
-        <v>873.813</v>
-      </c>
-      <c r="J9" s="45" t="n">
-        <v>67108864</v>
-      </c>
-      <c r="K9" s="45" t="inlineStr"/>
-      <c r="L9" s="45" t="n">
-        <v>65536</v>
-      </c>
-      <c r="M9" s="46" t="n">
-        <v>36.479</v>
-      </c>
-      <c r="N9" s="46" t="n">
-        <v>74.78189999999999</v>
-      </c>
-      <c r="O9" s="46" t="n">
-        <v>0.9728</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="44" t="inlineStr">
-        <is>
-          <t>1024-&gt;2048</t>
-        </is>
-      </c>
-      <c r="B10" s="45" t="n">
-        <v>524288</v>
-      </c>
-      <c r="C10" s="45" t="n">
-        <v>65536</v>
-      </c>
-      <c r="D10" s="46" t="n">
-        <v>1714.232</v>
-      </c>
-      <c r="E10" s="46" t="inlineStr"/>
-      <c r="F10" s="46" t="inlineStr"/>
-      <c r="G10" s="46" t="inlineStr"/>
-      <c r="H10" s="47" t="inlineStr"/>
-      <c r="I10" s="46" t="n">
-        <v>1747.627</v>
-      </c>
-      <c r="J10" s="45" t="n">
-        <v>134217728</v>
-      </c>
-      <c r="K10" s="45" t="inlineStr"/>
-      <c r="L10" s="45" t="n">
-        <v>131072</v>
-      </c>
-      <c r="M10" s="46" t="n">
-        <v>38.2305</v>
-      </c>
-      <c r="N10" s="46" t="n">
-        <v>78.37260000000001</v>
-      </c>
-      <c r="O10" s="46" t="n">
-        <v>1.0195</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="44" t="inlineStr">
-        <is>
-          <t>2048-&gt;4096</t>
-        </is>
-      </c>
-      <c r="B11" s="45" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="C11" s="45" t="n">
-        <v>131072</v>
-      </c>
-      <c r="D11" s="46" t="n">
-        <v>3596.599</v>
-      </c>
-      <c r="E11" s="46" t="inlineStr"/>
-      <c r="F11" s="46" t="inlineStr"/>
-      <c r="G11" s="46" t="inlineStr"/>
-      <c r="H11" s="47" t="inlineStr"/>
-      <c r="I11" s="46" t="n">
-        <v>3495.253</v>
-      </c>
-      <c r="J11" s="45" t="n">
-        <v>268435456</v>
-      </c>
-      <c r="K11" s="45" t="inlineStr"/>
-      <c r="L11" s="45" t="n">
-        <v>262144</v>
-      </c>
-      <c r="M11" s="46" t="n">
-        <v>36.4433</v>
-      </c>
-      <c r="N11" s="46" t="n">
-        <v>74.7088</v>
-      </c>
-      <c r="O11" s="46" t="n">
-        <v>0.9718</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="30" t="inlineStr">
-        <is>
-          <t>FIT</t>
-        </is>
-      </c>
-      <c r="B12" s="48" t="inlineStr"/>
-      <c r="C12" s="48" t="inlineStr"/>
-      <c r="D12" s="49" t="n">
-        <v>457.859</v>
-      </c>
-      <c r="E12" s="50" t="n">
-        <v>0.00337947</v>
-      </c>
-      <c r="F12" s="51" t="n">
-        <v>0.99991</v>
-      </c>
-      <c r="G12" s="49" t="inlineStr"/>
-      <c r="H12" s="52" t="n">
-        <v>4</v>
-      </c>
-      <c r="I12" s="49" t="inlineStr"/>
-      <c r="J12" s="48" t="inlineStr"/>
-      <c r="K12" s="48" t="inlineStr"/>
-      <c r="L12" s="48" t="inlineStr"/>
-      <c r="M12" s="49" t="n">
-        <v>36.9881</v>
-      </c>
-      <c r="N12" s="49" t="n">
-        <v>75.82550000000001</v>
-      </c>
-      <c r="O12" s="49" t="n">
-        <v>0.9863</v>
-      </c>
+      <c r="H23" s="25" t="n">
+        <v>1024</v>
+      </c>
+      <c r="I23" s="25" t="n">
+        <v>1966080</v>
+      </c>
+      <c r="J23" s="48" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="K23" s="48" t="n">
+        <v>7417.2</v>
+      </c>
+      <c r="L23" s="48" t="n">
+        <v>7400.7</v>
+      </c>
+      <c r="M23" s="48" t="n">
+        <v>93.58799999999999</v>
+      </c>
+      <c r="N23" s="48" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="O23" s="48" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="P23" s="48" t="n">
+        <v>289.5</v>
+      </c>
+      <c r="Q23" s="48" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="R23" s="48" t="n">
+        <v>141.371</v>
+      </c>
+      <c r="S23" s="48" t="n">
+        <v>0.9757</v>
+      </c>
+      <c r="T23" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="U23" s="48" t="n">
+        <v>512</v>
+      </c>
+      <c r="V23" s="48" t="n">
+        <v>0.5655</v>
+      </c>
+      <c r="W23" s="10" t="inlineStr"/>
+      <c r="X23" s="10" t="inlineStr"/>
+      <c r="Y23" s="10" t="inlineStr"/>
+      <c r="Z23" s="10" t="inlineStr"/>
+      <c r="AA23" s="10" t="inlineStr"/>
+      <c r="AB23" s="10" t="inlineStr"/>
+      <c r="AC23" s="10" t="inlineStr"/>
+      <c r="AD23" s="10" t="inlineStr"/>
+      <c r="AE23" s="10" t="inlineStr"/>
+      <c r="AF23" s="10" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8386,472 +11399,457 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>two2N sparsity 2:4 @ 300 MHz (floorplanned build)  -  source: sparse_2to4_300MHz.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="43" t="inlineStr">
-        <is>
-          <t>Rows 'a-&gt;b' are differentials between adjacent sizes (launch overhead cancels). Row 'FIT' is the least-squares fit: Best us = FIXED OVERHEAD, Mean us = slope in us/beat, Worst us = R^2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Size / pair</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Weight beats</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Rows</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Best us</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Mean us</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Worst us</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Spread %</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Reps</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>Ideal us</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>Bytes in</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>of which index</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>Bytes out</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>Mrow/s</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>GB/s</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>beats/cycle</t>
-        </is>
-      </c>
+          <t>Per-die resource split of the routed design - the floorplan, in numbers</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>From impl_1_slr_util_routed.rpt of the 300 MHz SLR build. ALL 512 DSPs sit in SLR1: the entire compute engine is on one die. SLR0 carries the movers, the HBM interconnect (276 BRAM tiles, 41%, the highest of any die) and all 16 PCIe transceivers. The 6,853 SLL crossings between SLR1 and SLR0 are the 17 AXIS kernel-to-kernel streams. No routed DCP survived the Vitis link, so a device screenshot is not available - this table is the evidence.  Source: GEMV_Floorplan_SLR.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>site_type</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>SLR0</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>SLR1</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>SLR2</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>SLR0_pct</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>SLR1_pct</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>SLR2_pct</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>holds</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>CLB</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="n">
+        <v>19261</v>
+      </c>
+      <c r="C4" s="25" t="n">
+        <v>20726</v>
+      </c>
+      <c r="D4" s="25" t="n">
+        <v>8372</v>
+      </c>
+      <c r="E4" s="48" t="n">
+        <v>35.05</v>
+      </c>
+      <c r="F4" s="48" t="n">
+        <v>38.38</v>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>1024</t>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>CLB LUTs</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>262144</v>
+        <v>69453</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>65536</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>1470.278</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>1618.479</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>1828.971</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="I5" s="11" t="n">
-        <v>873.813</v>
-      </c>
-      <c r="J5" s="25" t="n">
-        <v>92276736</v>
-      </c>
-      <c r="K5" s="25" t="n">
-        <v>25165824</v>
-      </c>
-      <c r="L5" s="25" t="n">
-        <v>131072</v>
-      </c>
-      <c r="M5" s="11" t="n">
-        <v>44.5739</v>
-      </c>
-      <c r="N5" s="11" t="n">
-        <v>62.8506</v>
-      </c>
-      <c r="O5" s="11" t="n">
-        <v>0.5943000000000001</v>
-      </c>
+        <v>113940</v>
+      </c>
+      <c r="D5" s="25" t="n">
+        <v>35362</v>
+      </c>
+      <c r="E5" s="48" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="F5" s="48" t="n">
+        <v>26.38</v>
+      </c>
+      <c r="G5" s="48" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="H5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>2048</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>LUT as Logic</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>524288</v>
+        <v>53540</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>131072</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>2492.261</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>2579.305</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>2740.292</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="I6" s="11" t="n">
-        <v>1747.627</v>
-      </c>
-      <c r="J6" s="25" t="n">
-        <v>184551424</v>
-      </c>
-      <c r="K6" s="25" t="n">
-        <v>50331648</v>
-      </c>
-      <c r="L6" s="25" t="n">
-        <v>262144</v>
-      </c>
-      <c r="M6" s="11" t="n">
-        <v>52.5916</v>
-      </c>
-      <c r="N6" s="11" t="n">
-        <v>74.155</v>
-      </c>
-      <c r="O6" s="11" t="n">
-        <v>0.7012</v>
-      </c>
+        <v>104211</v>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>32322</v>
+      </c>
+      <c r="E6" s="48" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="F6" s="48" t="n">
+        <v>24.12</v>
+      </c>
+      <c r="G6" s="48" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="H6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>4096</t>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>LUT as Memory</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
-        <v>1048576</v>
+        <v>15913</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>262144</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>4132.258</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>4314.617</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>4437.367</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>3495.253</v>
-      </c>
-      <c r="J7" s="25" t="n">
-        <v>369100800</v>
-      </c>
-      <c r="K7" s="25" t="n">
-        <v>100663296</v>
-      </c>
-      <c r="L7" s="25" t="n">
-        <v>524288</v>
-      </c>
-      <c r="M7" s="11" t="n">
-        <v>63.4384</v>
-      </c>
-      <c r="N7" s="11" t="n">
-        <v>89.4487</v>
-      </c>
-      <c r="O7" s="11" t="n">
-        <v>0.8458</v>
-      </c>
+        <v>9729</v>
+      </c>
+      <c r="D7" s="25" t="n">
+        <v>3040</v>
+      </c>
+      <c r="E7" s="48" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="F7" s="48" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="G7" s="48" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="H7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>8192</t>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>CLB Registers</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
-        <v>2097152</v>
+        <v>133849</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>524288</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>7774.47</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>7839.704</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>7887.112</v>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="I8" s="11" t="n">
-        <v>6990.507</v>
-      </c>
-      <c r="J8" s="25" t="n">
-        <v>738199552</v>
-      </c>
-      <c r="K8" s="25" t="n">
-        <v>201326592</v>
-      </c>
-      <c r="L8" s="25" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="M8" s="11" t="n">
-        <v>67.4371</v>
-      </c>
-      <c r="N8" s="11" t="n">
-        <v>95.0866</v>
-      </c>
-      <c r="O8" s="11" t="n">
-        <v>0.8992</v>
-      </c>
+        <v>133678</v>
+      </c>
+      <c r="D8" s="25" t="n">
+        <v>60953</v>
+      </c>
+      <c r="E8" s="48" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="F8" s="48" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="G8" s="48" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="H8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="44" t="inlineStr">
-        <is>
-          <t>1024-&gt;2048</t>
-        </is>
-      </c>
-      <c r="B9" s="45" t="n">
-        <v>262144</v>
-      </c>
-      <c r="C9" s="45" t="n">
-        <v>65536</v>
-      </c>
-      <c r="D9" s="46" t="n">
-        <v>1021.983</v>
-      </c>
-      <c r="E9" s="46" t="inlineStr"/>
-      <c r="F9" s="46" t="inlineStr"/>
-      <c r="G9" s="46" t="inlineStr"/>
-      <c r="H9" s="47" t="inlineStr"/>
-      <c r="I9" s="46" t="n">
-        <v>873.813</v>
-      </c>
-      <c r="J9" s="45" t="n">
-        <v>92274688</v>
-      </c>
-      <c r="K9" s="45" t="n">
-        <v>25165824</v>
-      </c>
-      <c r="L9" s="45" t="n">
-        <v>131072</v>
-      </c>
-      <c r="M9" s="46" t="n">
-        <v>64.1263</v>
-      </c>
-      <c r="N9" s="46" t="n">
-        <v>90.4181</v>
-      </c>
-      <c r="O9" s="46" t="n">
-        <v>0.855</v>
-      </c>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>CARRY8</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="n">
+        <v>1311</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>3357</v>
+      </c>
+      <c r="D9" s="48" t="n">
+        <v>313</v>
+      </c>
+      <c r="E9" s="48" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="F9" s="48" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="G9" s="48" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="44" t="inlineStr">
-        <is>
-          <t>2048-&gt;4096</t>
-        </is>
-      </c>
-      <c r="B10" s="45" t="n">
-        <v>524288</v>
-      </c>
-      <c r="C10" s="45" t="n">
-        <v>131072</v>
-      </c>
-      <c r="D10" s="46" t="n">
-        <v>1639.997</v>
-      </c>
-      <c r="E10" s="46" t="inlineStr"/>
-      <c r="F10" s="46" t="inlineStr"/>
-      <c r="G10" s="46" t="inlineStr"/>
-      <c r="H10" s="47" t="inlineStr"/>
-      <c r="I10" s="46" t="n">
-        <v>1747.627</v>
-      </c>
-      <c r="J10" s="45" t="n">
-        <v>184549376</v>
-      </c>
-      <c r="K10" s="45" t="n">
-        <v>50331648</v>
-      </c>
-      <c r="L10" s="45" t="n">
-        <v>262144</v>
-      </c>
-      <c r="M10" s="46" t="n">
-        <v>79.9221</v>
-      </c>
-      <c r="N10" s="46" t="n">
-        <v>112.6902</v>
-      </c>
-      <c r="O10" s="46" t="n">
-        <v>1.0656</v>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>F7 Muxes</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="n">
+        <v>3143</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>8843</v>
+      </c>
+      <c r="D10" s="25" t="n">
+        <v>1054</v>
+      </c>
+      <c r="E10" s="48" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F10" s="48" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G10" s="48" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>8192 of SLR1's are the sparse gather muxes</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="44" t="inlineStr">
-        <is>
-          <t>4096-&gt;8192</t>
-        </is>
-      </c>
-      <c r="B11" s="45" t="n">
-        <v>1048576</v>
-      </c>
-      <c r="C11" s="45" t="n">
-        <v>262144</v>
-      </c>
-      <c r="D11" s="46" t="n">
-        <v>3642.212</v>
-      </c>
-      <c r="E11" s="46" t="inlineStr"/>
-      <c r="F11" s="46" t="inlineStr"/>
-      <c r="G11" s="46" t="inlineStr"/>
-      <c r="H11" s="47" t="inlineStr"/>
-      <c r="I11" s="46" t="n">
-        <v>3495.253</v>
-      </c>
-      <c r="J11" s="45" t="n">
-        <v>369098752</v>
-      </c>
-      <c r="K11" s="45" t="n">
-        <v>100663296</v>
-      </c>
-      <c r="L11" s="45" t="n">
-        <v>524288</v>
-      </c>
-      <c r="M11" s="46" t="n">
-        <v>71.9738</v>
-      </c>
-      <c r="N11" s="46" t="n">
-        <v>101.4831</v>
-      </c>
-      <c r="O11" s="46" t="n">
-        <v>0.9597</v>
-      </c>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>F8 Muxes</t>
+        </is>
+      </c>
+      <c r="B11" s="48" t="n">
+        <v>16</v>
+      </c>
+      <c r="C11" s="48" t="n">
+        <v>141</v>
+      </c>
+      <c r="D11" s="48" t="n">
+        <v>47</v>
+      </c>
+      <c r="E11" s="48" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F11" s="48" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G11" s="48" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="inlineStr">
-        <is>
-          <t>FIT</t>
-        </is>
-      </c>
-      <c r="B12" s="48" t="inlineStr"/>
-      <c r="C12" s="48" t="inlineStr"/>
-      <c r="D12" s="49" t="n">
-        <v>619.077</v>
-      </c>
-      <c r="E12" s="50" t="n">
-        <v>0.00340601</v>
-      </c>
-      <c r="F12" s="51" t="n">
-        <v>0.99944</v>
-      </c>
-      <c r="G12" s="49" t="inlineStr"/>
-      <c r="H12" s="52" t="n">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Block RAM Tile</t>
+        </is>
+      </c>
+      <c r="B12" s="48" t="n">
+        <v>276</v>
+      </c>
+      <c r="C12" s="48" t="n">
+        <v>154.5</v>
+      </c>
+      <c r="D12" s="48" t="n">
+        <v>94</v>
+      </c>
+      <c r="E12" s="48" t="n">
+        <v>41.07</v>
+      </c>
+      <c r="F12" s="48" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="G12" s="48" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>SLR0 highest (41%) = mover FIFOs + HBM interconnect</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>URAM</t>
+        </is>
+      </c>
+      <c r="B13" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>DSPs</t>
+        </is>
+      </c>
+      <c r="B14" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="48" t="n">
+        <v>512</v>
+      </c>
+      <c r="D14" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="I12" s="49" t="inlineStr"/>
-      <c r="J12" s="48" t="inlineStr"/>
-      <c r="K12" s="48" t="inlineStr"/>
-      <c r="L12" s="48" t="inlineStr"/>
-      <c r="M12" s="49" t="n">
-        <v>73.3998</v>
-      </c>
-      <c r="N12" s="49" t="n">
-        <v>103.4937</v>
-      </c>
-      <c r="O12" s="49" t="n">
-        <v>0.9787</v>
-      </c>
+      <c r="E14" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="48" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="G14" s="48" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>ALL 512 in SLR1 = the entire GEMV engine, one die</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>GTs</t>
+        </is>
+      </c>
+      <c r="B15" s="48" t="n">
+        <v>16</v>
+      </c>
+      <c r="C15" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="10" t="inlineStr"/>
+      <c r="F15" s="10" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr"/>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>SLR0 only = PCIe transceivers</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>SLL SLR1&lt;-&gt;SLR0</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr"/>
+      <c r="C16" s="25" t="n">
+        <v>6853</v>
+      </c>
+      <c r="D16" s="10" t="inlineStr"/>
+      <c r="E16" s="10" t="inlineStr"/>
+      <c r="F16" s="10" t="inlineStr"/>
+      <c r="G16" s="10" t="inlineStr"/>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>the 17 AXIS kernel-to-kernel streams</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>SLL SLR2&lt;-&gt;SLR1</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr"/>
+      <c r="C17" s="25" t="n">
+        <v>3993</v>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
+      <c r="E17" s="10" t="inlineStr"/>
+      <c r="F17" s="10" t="inlineStr"/>
+      <c r="G17" s="10" t="inlineStr"/>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>platform, not ours</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>SLL total</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr"/>
+      <c r="C18" s="25" t="n">
+        <v>10846</v>
+      </c>
+      <c r="D18" s="10" t="inlineStr"/>
+      <c r="E18" s="10" t="inlineStr"/>
+      <c r="F18" s="10" t="inlineStr"/>
+      <c r="G18" s="10" t="inlineStr"/>
+      <c r="H18" s="10" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>